--- a/data/ams_weekly_data/Nexlev/ads_report_week10.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5715E210-71C1-4E51-A796-51260FF2051F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45432B3-3EFD-4F65-BB39-23CD982B7B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
   </bookViews>
   <sheets>
     <sheet name="SP" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6303" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7491" uniqueCount="322">
   <si>
     <t>No Portfolio</t>
   </si>
@@ -869,6 +869,147 @@
   <si>
     <t>B0DTYDTKN8</t>
   </si>
+  <si>
+    <t>HPC _  Women Trimmers</t>
+  </si>
+  <si>
+    <t>H&amp;K_Cleaning Vacuum - SS/SPM/SM Series</t>
+  </si>
+  <si>
+    <t>Nex_HPC_SBV_KW_V-02_TBM_vCPM</t>
+  </si>
+  <si>
+    <t>Nex_HPC_T-02_SBV_Reel</t>
+  </si>
+  <si>
+    <t>Nex_HnK_VC-05_SBV_KW_CPM</t>
+  </si>
+  <si>
+    <t>Nex_HPC_SBV_HSB-03_Tavishi Video_vCPM</t>
+  </si>
+  <si>
+    <t>HnK_Nexlev SBV | KT | AP-03 - Reel</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT |SC-04 |Foldable Steam Cleaner|-B0DNJS23HS</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT | KE-01 -Electric Food Kettle</t>
+  </si>
+  <si>
+    <t>HnK_SBV_Dust Mite_KT_BMC_MR-01</t>
+  </si>
+  <si>
+    <t>SBV |KT| SPM-01 - B0DTYDTKN8 - Phrase</t>
+  </si>
+  <si>
+    <t>HnK_Nexlev_SBV_Reach_KT_GS-02 (GS Storepage)</t>
+  </si>
+  <si>
+    <t>HnK_SB | SC-01| SC-05|SC-04-Steam Cleaner_KW_Exact</t>
+  </si>
+  <si>
+    <t>HnK_SBV| KT | SC-01 - B0CDPP45BM</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT | VC-01 - B0DCGHVN81</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT | MR-02 - B0DCK7ZH5P</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT | SC-04 - Steam Cleaner (B0DNJS23HS)</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT | HU-01 - B0DVC968P1 - Reel</t>
+  </si>
+  <si>
+    <t>SBV | KT | MR-02 - (B0DCK7ZH5P) - VCPM</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | CR-01 - (B0D2LHNS9B)</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | CM-01 - B0DFCDKMWR</t>
+  </si>
+  <si>
+    <t>Hnk_SBV | KT | MR-02 - B0DCK7ZH5P - Reel</t>
+  </si>
+  <si>
+    <t>SBV | KT | GS-02 - B0CDPMX152 - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | V-01 (RG) - B0DQ8W1RBV</t>
+  </si>
+  <si>
+    <t>HnK_Nexlev SBV | KT | AP-03 - B0DVC58QPZ</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | V-03 | B0DQCWRG3H</t>
+  </si>
+  <si>
+    <t>HnK_Nexlev SBV | KT | MR-01 - B0CYSLCRQS - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | HSB-04 - B0DCK3N2JJ</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT | SC-05 - Steam Cleaner - B0F43P6D23 - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | HSB-04 - B0DCK3N2JJ - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | EA-01 - B0D67727VG - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | CFM-01 - B0DM6BB3VT - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | EA-02 - B0DKK15YNJ - Reel</t>
+  </si>
+  <si>
+    <t>SBV | KT | ST-01 - B0DVC7VJP1</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | V-01 (RG) - B0DQ8W1RBV - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT | LE-02 - B0DCGHKRXX - Reel</t>
+  </si>
+  <si>
+    <t>HnK_Nexlev SBV | KT | AP-03 - B0DVC58QPZ (NEW)</t>
+  </si>
+  <si>
+    <t>HPC_SBV |KT| CM-01 - B0DFCDKMWR</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT | ST-01 - B0DVC7VJP1 - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV_KT_B0D9KFZYG8_FS-01</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT |SC-04 | B0DNJS23HS - Reel</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT | VC-01 - B0DCGHVN81 - Reel</t>
+  </si>
+  <si>
+    <t>HPC_SBV | KT| HSB-04 - B0DCK3N2JJ - Reel</t>
+  </si>
+  <si>
+    <t>HnK_SBV | KT |SC-04 | B0DNJS23HS -Reel</t>
+  </si>
+  <si>
+    <t>Hnk_SBV | KT | V-03 - B0DQCWRG3H - Reel</t>
+  </si>
+  <si>
+    <t>B0D2LD6BYJ</t>
+  </si>
+  <si>
+    <t>B0DVC968P1</t>
+  </si>
 </sst>
 </file>
 
@@ -1227,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EF6D63-3663-4E20-A7FC-263D078FDDB8}">
-  <dimension ref="A1:I1204"/>
+  <dimension ref="A1:I1501"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
@@ -36147,6 +36288,8619 @@
         <v>2</v>
       </c>
       <c r="I1204" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1205" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1205">
+        <v>0</v>
+      </c>
+      <c r="E1205">
+        <v>0</v>
+      </c>
+      <c r="F1205">
+        <v>0</v>
+      </c>
+      <c r="G1205">
+        <v>0</v>
+      </c>
+      <c r="H1205">
+        <v>0</v>
+      </c>
+      <c r="I1205" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1206" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1206">
+        <v>0</v>
+      </c>
+      <c r="E1206">
+        <v>0</v>
+      </c>
+      <c r="F1206">
+        <v>0</v>
+      </c>
+      <c r="G1206">
+        <v>0</v>
+      </c>
+      <c r="H1206">
+        <v>0</v>
+      </c>
+      <c r="I1206" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1207" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1207">
+        <v>0</v>
+      </c>
+      <c r="E1207">
+        <v>0</v>
+      </c>
+      <c r="F1207">
+        <v>0</v>
+      </c>
+      <c r="G1207">
+        <v>0</v>
+      </c>
+      <c r="H1207">
+        <v>0</v>
+      </c>
+      <c r="I1207" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1208" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1208">
+        <v>0</v>
+      </c>
+      <c r="E1208">
+        <v>0</v>
+      </c>
+      <c r="F1208">
+        <v>0</v>
+      </c>
+      <c r="G1208">
+        <v>0</v>
+      </c>
+      <c r="H1208">
+        <v>0</v>
+      </c>
+      <c r="I1208" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1209" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1209">
+        <v>0</v>
+      </c>
+      <c r="E1209">
+        <v>0</v>
+      </c>
+      <c r="F1209">
+        <v>0</v>
+      </c>
+      <c r="G1209">
+        <v>0</v>
+      </c>
+      <c r="H1209">
+        <v>0</v>
+      </c>
+      <c r="I1209" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1210" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1210">
+        <v>0</v>
+      </c>
+      <c r="E1210">
+        <v>0</v>
+      </c>
+      <c r="F1210">
+        <v>0</v>
+      </c>
+      <c r="G1210">
+        <v>0</v>
+      </c>
+      <c r="H1210">
+        <v>0</v>
+      </c>
+      <c r="I1210" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1211" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1211">
+        <v>0</v>
+      </c>
+      <c r="E1211">
+        <v>0</v>
+      </c>
+      <c r="F1211">
+        <v>0</v>
+      </c>
+      <c r="G1211">
+        <v>0</v>
+      </c>
+      <c r="H1211">
+        <v>0</v>
+      </c>
+      <c r="I1211" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1212" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1212">
+        <v>0</v>
+      </c>
+      <c r="E1212">
+        <v>0</v>
+      </c>
+      <c r="F1212">
+        <v>0</v>
+      </c>
+      <c r="G1212">
+        <v>0</v>
+      </c>
+      <c r="H1212">
+        <v>0</v>
+      </c>
+      <c r="I1212" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1213" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1213">
+        <v>0</v>
+      </c>
+      <c r="E1213">
+        <v>0</v>
+      </c>
+      <c r="F1213">
+        <v>0</v>
+      </c>
+      <c r="G1213">
+        <v>0</v>
+      </c>
+      <c r="H1213">
+        <v>0</v>
+      </c>
+      <c r="I1213" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1214" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1214">
+        <v>0</v>
+      </c>
+      <c r="E1214">
+        <v>0</v>
+      </c>
+      <c r="F1214">
+        <v>0</v>
+      </c>
+      <c r="G1214">
+        <v>0</v>
+      </c>
+      <c r="H1214">
+        <v>0</v>
+      </c>
+      <c r="I1214" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1215" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1215">
+        <v>0</v>
+      </c>
+      <c r="E1215">
+        <v>0</v>
+      </c>
+      <c r="F1215">
+        <v>0</v>
+      </c>
+      <c r="G1215">
+        <v>0</v>
+      </c>
+      <c r="H1215">
+        <v>0</v>
+      </c>
+      <c r="I1215" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1216" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1216">
+        <v>0</v>
+      </c>
+      <c r="E1216">
+        <v>0</v>
+      </c>
+      <c r="F1216">
+        <v>0</v>
+      </c>
+      <c r="G1216">
+        <v>0</v>
+      </c>
+      <c r="H1216">
+        <v>0</v>
+      </c>
+      <c r="I1216" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1217" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1217">
+        <v>0</v>
+      </c>
+      <c r="E1217">
+        <v>0</v>
+      </c>
+      <c r="F1217">
+        <v>0</v>
+      </c>
+      <c r="G1217">
+        <v>0</v>
+      </c>
+      <c r="H1217">
+        <v>0</v>
+      </c>
+      <c r="I1217" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1218" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1218">
+        <v>0</v>
+      </c>
+      <c r="E1218">
+        <v>0</v>
+      </c>
+      <c r="F1218">
+        <v>0</v>
+      </c>
+      <c r="G1218">
+        <v>0</v>
+      </c>
+      <c r="H1218">
+        <v>0</v>
+      </c>
+      <c r="I1218" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1219" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1219">
+        <v>53</v>
+      </c>
+      <c r="E1219">
+        <v>0</v>
+      </c>
+      <c r="F1219">
+        <v>17.33221</v>
+      </c>
+      <c r="G1219">
+        <v>0</v>
+      </c>
+      <c r="H1219">
+        <v>0</v>
+      </c>
+      <c r="I1219" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1220" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1220">
+        <v>33</v>
+      </c>
+      <c r="E1220">
+        <v>0</v>
+      </c>
+      <c r="F1220">
+        <v>7.00366</v>
+      </c>
+      <c r="G1220">
+        <v>0</v>
+      </c>
+      <c r="H1220">
+        <v>0</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1221" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1221">
+        <v>39</v>
+      </c>
+      <c r="E1221">
+        <v>1</v>
+      </c>
+      <c r="F1221">
+        <v>11.80616</v>
+      </c>
+      <c r="G1221">
+        <v>0</v>
+      </c>
+      <c r="H1221">
+        <v>0</v>
+      </c>
+      <c r="I1221" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1222" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1222">
+        <v>25</v>
+      </c>
+      <c r="E1222">
+        <v>0</v>
+      </c>
+      <c r="F1222">
+        <v>8.4</v>
+      </c>
+      <c r="G1222">
+        <v>0</v>
+      </c>
+      <c r="H1222">
+        <v>0</v>
+      </c>
+      <c r="I1222" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1223" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1223">
+        <v>29</v>
+      </c>
+      <c r="E1223">
+        <v>2</v>
+      </c>
+      <c r="F1223">
+        <v>11.62363</v>
+      </c>
+      <c r="G1223">
+        <v>0</v>
+      </c>
+      <c r="H1223">
+        <v>0</v>
+      </c>
+      <c r="I1223" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1224" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1224">
+        <v>28</v>
+      </c>
+      <c r="E1224">
+        <v>1</v>
+      </c>
+      <c r="F1224">
+        <v>8.2135499999999997</v>
+      </c>
+      <c r="G1224">
+        <v>0</v>
+      </c>
+      <c r="H1224">
+        <v>0</v>
+      </c>
+      <c r="I1224" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1225" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1225">
+        <v>17</v>
+      </c>
+      <c r="E1225">
+        <v>0</v>
+      </c>
+      <c r="F1225">
+        <v>6</v>
+      </c>
+      <c r="G1225">
+        <v>0</v>
+      </c>
+      <c r="H1225">
+        <v>0</v>
+      </c>
+      <c r="I1225" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1226" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1226">
+        <v>60</v>
+      </c>
+      <c r="E1226">
+        <v>4</v>
+      </c>
+      <c r="F1226">
+        <v>8.5746300000000009</v>
+      </c>
+      <c r="G1226">
+        <v>0</v>
+      </c>
+      <c r="H1226">
+        <v>0</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1227" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1227">
+        <v>85</v>
+      </c>
+      <c r="E1227">
+        <v>1</v>
+      </c>
+      <c r="F1227">
+        <v>12.925700000000001</v>
+      </c>
+      <c r="G1227">
+        <v>0</v>
+      </c>
+      <c r="H1227">
+        <v>0</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1228" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1228">
+        <v>73</v>
+      </c>
+      <c r="E1228">
+        <v>2</v>
+      </c>
+      <c r="F1228">
+        <v>9.5145599999999995</v>
+      </c>
+      <c r="G1228">
+        <v>0</v>
+      </c>
+      <c r="H1228">
+        <v>0</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1229" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1229">
+        <v>208</v>
+      </c>
+      <c r="E1229">
+        <v>5</v>
+      </c>
+      <c r="F1229">
+        <v>37.447690000000001</v>
+      </c>
+      <c r="G1229">
+        <v>0</v>
+      </c>
+      <c r="H1229">
+        <v>0</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1230" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1230">
+        <v>265</v>
+      </c>
+      <c r="E1230">
+        <v>3</v>
+      </c>
+      <c r="F1230">
+        <v>42.682209999999998</v>
+      </c>
+      <c r="G1230">
+        <v>0</v>
+      </c>
+      <c r="H1230">
+        <v>0</v>
+      </c>
+      <c r="I1230" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1231" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1231">
+        <v>465</v>
+      </c>
+      <c r="E1231">
+        <v>14</v>
+      </c>
+      <c r="F1231">
+        <v>128.85536999999999</v>
+      </c>
+      <c r="G1231">
+        <v>0</v>
+      </c>
+      <c r="H1231">
+        <v>0</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1232" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1232">
+        <v>699</v>
+      </c>
+      <c r="E1232">
+        <v>12</v>
+      </c>
+      <c r="F1232">
+        <v>243.38179</v>
+      </c>
+      <c r="G1232">
+        <v>0</v>
+      </c>
+      <c r="H1232">
+        <v>0</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1233" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1233">
+        <v>81</v>
+      </c>
+      <c r="E1233">
+        <v>4</v>
+      </c>
+      <c r="F1233">
+        <v>115.99</v>
+      </c>
+      <c r="G1233">
+        <v>0</v>
+      </c>
+      <c r="H1233">
+        <v>0</v>
+      </c>
+      <c r="I1233" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1234" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1234">
+        <v>30</v>
+      </c>
+      <c r="E1234">
+        <v>3</v>
+      </c>
+      <c r="F1234">
+        <v>82.04</v>
+      </c>
+      <c r="G1234">
+        <v>0</v>
+      </c>
+      <c r="H1234">
+        <v>0</v>
+      </c>
+      <c r="I1234" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1235" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1235">
+        <v>996</v>
+      </c>
+      <c r="E1235">
+        <v>17</v>
+      </c>
+      <c r="F1235">
+        <v>293.92</v>
+      </c>
+      <c r="G1235">
+        <v>0</v>
+      </c>
+      <c r="H1235">
+        <v>0</v>
+      </c>
+      <c r="I1235" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1236" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1236">
+        <v>1122</v>
+      </c>
+      <c r="E1236">
+        <v>23</v>
+      </c>
+      <c r="F1236">
+        <v>376.27</v>
+      </c>
+      <c r="G1236">
+        <v>2604.2399999999998</v>
+      </c>
+      <c r="H1236">
+        <v>1</v>
+      </c>
+      <c r="I1236" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1237" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1237">
+        <v>3506</v>
+      </c>
+      <c r="E1237">
+        <v>45</v>
+      </c>
+      <c r="F1237">
+        <v>787.75</v>
+      </c>
+      <c r="G1237">
+        <v>0</v>
+      </c>
+      <c r="H1237">
+        <v>0</v>
+      </c>
+      <c r="I1237" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1238" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1238">
+        <v>1144</v>
+      </c>
+      <c r="E1238">
+        <v>20</v>
+      </c>
+      <c r="F1238">
+        <v>409.38</v>
+      </c>
+      <c r="G1238">
+        <v>0</v>
+      </c>
+      <c r="H1238">
+        <v>0</v>
+      </c>
+      <c r="I1238" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1239" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1239">
+        <v>2136</v>
+      </c>
+      <c r="E1239">
+        <v>40</v>
+      </c>
+      <c r="F1239">
+        <v>774.17</v>
+      </c>
+      <c r="G1239">
+        <v>0</v>
+      </c>
+      <c r="H1239">
+        <v>0</v>
+      </c>
+      <c r="I1239" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1240" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1240">
+        <v>2378</v>
+      </c>
+      <c r="E1240">
+        <v>39</v>
+      </c>
+      <c r="F1240">
+        <v>854.74</v>
+      </c>
+      <c r="G1240">
+        <v>0</v>
+      </c>
+      <c r="H1240">
+        <v>0</v>
+      </c>
+      <c r="I1240" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1241" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1241">
+        <v>6801</v>
+      </c>
+      <c r="E1241">
+        <v>128</v>
+      </c>
+      <c r="F1241">
+        <v>1812.57</v>
+      </c>
+      <c r="G1241">
+        <v>0</v>
+      </c>
+      <c r="H1241">
+        <v>0</v>
+      </c>
+      <c r="I1241" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1242" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1242">
+        <v>3183</v>
+      </c>
+      <c r="E1242">
+        <v>64</v>
+      </c>
+      <c r="F1242">
+        <v>868.57</v>
+      </c>
+      <c r="G1242">
+        <v>0</v>
+      </c>
+      <c r="H1242">
+        <v>0</v>
+      </c>
+      <c r="I1242" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1243" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1243">
+        <v>0</v>
+      </c>
+      <c r="E1243">
+        <v>0</v>
+      </c>
+      <c r="F1243">
+        <v>0</v>
+      </c>
+      <c r="G1243">
+        <v>0</v>
+      </c>
+      <c r="H1243">
+        <v>0</v>
+      </c>
+      <c r="I1243" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1244" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1244">
+        <v>118</v>
+      </c>
+      <c r="E1244">
+        <v>2</v>
+      </c>
+      <c r="F1244">
+        <v>15.09</v>
+      </c>
+      <c r="G1244">
+        <v>0</v>
+      </c>
+      <c r="H1244">
+        <v>0</v>
+      </c>
+      <c r="I1244" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1245" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1245">
+        <v>239</v>
+      </c>
+      <c r="E1245">
+        <v>2</v>
+      </c>
+      <c r="F1245">
+        <v>8.81</v>
+      </c>
+      <c r="G1245">
+        <v>0</v>
+      </c>
+      <c r="H1245">
+        <v>0</v>
+      </c>
+      <c r="I1245" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1246" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1246">
+        <v>466</v>
+      </c>
+      <c r="E1246">
+        <v>4</v>
+      </c>
+      <c r="F1246">
+        <v>19.690000000000001</v>
+      </c>
+      <c r="G1246">
+        <v>0</v>
+      </c>
+      <c r="H1246">
+        <v>0</v>
+      </c>
+      <c r="I1246" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1247" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1247">
+        <v>0</v>
+      </c>
+      <c r="E1247">
+        <v>0</v>
+      </c>
+      <c r="F1247">
+        <v>0</v>
+      </c>
+      <c r="G1247">
+        <v>0</v>
+      </c>
+      <c r="H1247">
+        <v>0</v>
+      </c>
+      <c r="I1247" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1248" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1248">
+        <v>349</v>
+      </c>
+      <c r="E1248">
+        <v>6</v>
+      </c>
+      <c r="F1248">
+        <v>51.97</v>
+      </c>
+      <c r="G1248">
+        <v>0</v>
+      </c>
+      <c r="H1248">
+        <v>0</v>
+      </c>
+      <c r="I1248" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1249" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1249">
+        <v>149</v>
+      </c>
+      <c r="E1249">
+        <v>0</v>
+      </c>
+      <c r="F1249">
+        <v>0</v>
+      </c>
+      <c r="G1249">
+        <v>0</v>
+      </c>
+      <c r="H1249">
+        <v>0</v>
+      </c>
+      <c r="I1249" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1250" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1250">
+        <v>105</v>
+      </c>
+      <c r="E1250">
+        <v>4</v>
+      </c>
+      <c r="F1250">
+        <v>119.16</v>
+      </c>
+      <c r="G1250">
+        <v>0</v>
+      </c>
+      <c r="H1250">
+        <v>0</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1251" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1251">
+        <v>256</v>
+      </c>
+      <c r="E1251">
+        <v>16</v>
+      </c>
+      <c r="F1251">
+        <v>367.91</v>
+      </c>
+      <c r="G1251">
+        <v>0</v>
+      </c>
+      <c r="H1251">
+        <v>0</v>
+      </c>
+      <c r="I1251" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1252" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1252">
+        <v>250</v>
+      </c>
+      <c r="E1252">
+        <v>9</v>
+      </c>
+      <c r="F1252">
+        <v>107.26</v>
+      </c>
+      <c r="G1252">
+        <v>0</v>
+      </c>
+      <c r="H1252">
+        <v>0</v>
+      </c>
+      <c r="I1252" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1253" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1253">
+        <v>326</v>
+      </c>
+      <c r="E1253">
+        <v>17</v>
+      </c>
+      <c r="F1253">
+        <v>206.47</v>
+      </c>
+      <c r="G1253">
+        <v>0</v>
+      </c>
+      <c r="H1253">
+        <v>0</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1254" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1254">
+        <v>492</v>
+      </c>
+      <c r="E1254">
+        <v>21</v>
+      </c>
+      <c r="F1254">
+        <v>256.45</v>
+      </c>
+      <c r="G1254">
+        <v>2456.7800000000002</v>
+      </c>
+      <c r="H1254">
+        <v>2</v>
+      </c>
+      <c r="I1254" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1255" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1255">
+        <v>389</v>
+      </c>
+      <c r="E1255">
+        <v>18</v>
+      </c>
+      <c r="F1255">
+        <v>219.8</v>
+      </c>
+      <c r="G1255">
+        <v>0</v>
+      </c>
+      <c r="H1255">
+        <v>0</v>
+      </c>
+      <c r="I1255" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1256" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1256">
+        <v>530</v>
+      </c>
+      <c r="E1256">
+        <v>11</v>
+      </c>
+      <c r="F1256">
+        <v>146.04</v>
+      </c>
+      <c r="G1256">
+        <v>2431.37</v>
+      </c>
+      <c r="H1256">
+        <v>1</v>
+      </c>
+      <c r="I1256" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1257" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1257">
+        <v>0</v>
+      </c>
+      <c r="E1257">
+        <v>0</v>
+      </c>
+      <c r="F1257">
+        <v>0</v>
+      </c>
+      <c r="G1257">
+        <v>0</v>
+      </c>
+      <c r="H1257">
+        <v>0</v>
+      </c>
+      <c r="I1257" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1258" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1258">
+        <v>0</v>
+      </c>
+      <c r="E1258">
+        <v>0</v>
+      </c>
+      <c r="F1258">
+        <v>0</v>
+      </c>
+      <c r="G1258">
+        <v>0</v>
+      </c>
+      <c r="H1258">
+        <v>0</v>
+      </c>
+      <c r="I1258" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1259" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1259">
+        <v>0</v>
+      </c>
+      <c r="E1259">
+        <v>0</v>
+      </c>
+      <c r="F1259">
+        <v>0</v>
+      </c>
+      <c r="G1259">
+        <v>0</v>
+      </c>
+      <c r="H1259">
+        <v>0</v>
+      </c>
+      <c r="I1259" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1260" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1260">
+        <v>0</v>
+      </c>
+      <c r="E1260">
+        <v>0</v>
+      </c>
+      <c r="F1260">
+        <v>0</v>
+      </c>
+      <c r="G1260">
+        <v>0</v>
+      </c>
+      <c r="H1260">
+        <v>0</v>
+      </c>
+      <c r="I1260" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1261" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1261">
+        <v>0</v>
+      </c>
+      <c r="E1261">
+        <v>0</v>
+      </c>
+      <c r="F1261">
+        <v>0</v>
+      </c>
+      <c r="G1261">
+        <v>0</v>
+      </c>
+      <c r="H1261">
+        <v>0</v>
+      </c>
+      <c r="I1261" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1262" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1262">
+        <v>0</v>
+      </c>
+      <c r="E1262">
+        <v>0</v>
+      </c>
+      <c r="F1262">
+        <v>0</v>
+      </c>
+      <c r="G1262">
+        <v>0</v>
+      </c>
+      <c r="H1262">
+        <v>0</v>
+      </c>
+      <c r="I1262" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1263" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1263">
+        <v>0</v>
+      </c>
+      <c r="E1263">
+        <v>0</v>
+      </c>
+      <c r="F1263">
+        <v>0</v>
+      </c>
+      <c r="G1263">
+        <v>0</v>
+      </c>
+      <c r="H1263">
+        <v>0</v>
+      </c>
+      <c r="I1263" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1264" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1264">
+        <v>2706</v>
+      </c>
+      <c r="E1264">
+        <v>58</v>
+      </c>
+      <c r="F1264">
+        <v>612.0326</v>
+      </c>
+      <c r="G1264">
+        <v>0</v>
+      </c>
+      <c r="H1264">
+        <v>0</v>
+      </c>
+      <c r="I1264" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1265" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1265">
+        <v>3052</v>
+      </c>
+      <c r="E1265">
+        <v>54</v>
+      </c>
+      <c r="F1265">
+        <v>713.77077999999995</v>
+      </c>
+      <c r="G1265">
+        <v>0</v>
+      </c>
+      <c r="H1265">
+        <v>0</v>
+      </c>
+      <c r="I1265" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1266" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1266">
+        <v>359</v>
+      </c>
+      <c r="E1266">
+        <v>12</v>
+      </c>
+      <c r="F1266">
+        <v>100.81878</v>
+      </c>
+      <c r="G1266">
+        <v>0</v>
+      </c>
+      <c r="H1266">
+        <v>0</v>
+      </c>
+      <c r="I1266" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1267" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1267">
+        <v>1827</v>
+      </c>
+      <c r="E1267">
+        <v>30</v>
+      </c>
+      <c r="F1267">
+        <v>341.74633</v>
+      </c>
+      <c r="G1267">
+        <v>0</v>
+      </c>
+      <c r="H1267">
+        <v>0</v>
+      </c>
+      <c r="I1267" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1268" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1268">
+        <v>1718</v>
+      </c>
+      <c r="E1268">
+        <v>13</v>
+      </c>
+      <c r="F1268">
+        <v>320.60255999999998</v>
+      </c>
+      <c r="G1268">
+        <v>0</v>
+      </c>
+      <c r="H1268">
+        <v>0</v>
+      </c>
+      <c r="I1268" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1269" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1269">
+        <v>1680</v>
+      </c>
+      <c r="E1269">
+        <v>20</v>
+      </c>
+      <c r="F1269">
+        <v>320.03751</v>
+      </c>
+      <c r="G1269">
+        <v>0</v>
+      </c>
+      <c r="H1269">
+        <v>0</v>
+      </c>
+      <c r="I1269" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1270" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1270">
+        <v>2345</v>
+      </c>
+      <c r="E1270">
+        <v>48</v>
+      </c>
+      <c r="F1270">
+        <v>433.43079999999998</v>
+      </c>
+      <c r="G1270">
+        <v>0</v>
+      </c>
+      <c r="H1270">
+        <v>0</v>
+      </c>
+      <c r="I1270" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1271" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1271">
+        <v>19695</v>
+      </c>
+      <c r="E1271">
+        <v>127</v>
+      </c>
+      <c r="F1271">
+        <v>2160.96</v>
+      </c>
+      <c r="G1271">
+        <v>22828.81</v>
+      </c>
+      <c r="H1271">
+        <v>8</v>
+      </c>
+      <c r="I1271" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1272" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1272">
+        <v>23554</v>
+      </c>
+      <c r="E1272">
+        <v>150</v>
+      </c>
+      <c r="F1272">
+        <v>2361.84</v>
+      </c>
+      <c r="G1272">
+        <v>25332.18</v>
+      </c>
+      <c r="H1272">
+        <v>8</v>
+      </c>
+      <c r="I1272" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1273" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1273">
+        <v>19279</v>
+      </c>
+      <c r="E1273">
+        <v>86</v>
+      </c>
+      <c r="F1273">
+        <v>1422.22</v>
+      </c>
+      <c r="G1273">
+        <v>19402.54</v>
+      </c>
+      <c r="H1273">
+        <v>5</v>
+      </c>
+      <c r="I1273" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1274" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1274">
+        <v>18661</v>
+      </c>
+      <c r="E1274">
+        <v>126</v>
+      </c>
+      <c r="F1274">
+        <v>2102.11</v>
+      </c>
+      <c r="G1274">
+        <v>7419.5</v>
+      </c>
+      <c r="H1274">
+        <v>3</v>
+      </c>
+      <c r="I1274" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1275" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1275">
+        <v>13806</v>
+      </c>
+      <c r="E1275">
+        <v>114</v>
+      </c>
+      <c r="F1275">
+        <v>2254.34</v>
+      </c>
+      <c r="G1275">
+        <v>22788.98</v>
+      </c>
+      <c r="H1275">
+        <v>8</v>
+      </c>
+      <c r="I1275" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1276" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1276">
+        <v>20357</v>
+      </c>
+      <c r="E1276">
+        <v>116</v>
+      </c>
+      <c r="F1276">
+        <v>1966.2</v>
+      </c>
+      <c r="G1276">
+        <v>7927.96</v>
+      </c>
+      <c r="H1276">
+        <v>3</v>
+      </c>
+      <c r="I1276" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1277" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1277">
+        <v>22775</v>
+      </c>
+      <c r="E1277">
+        <v>142</v>
+      </c>
+      <c r="F1277">
+        <v>2402.98</v>
+      </c>
+      <c r="G1277">
+        <v>19061.849999999999</v>
+      </c>
+      <c r="H1277">
+        <v>5</v>
+      </c>
+      <c r="I1277" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1278" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1278">
+        <v>0</v>
+      </c>
+      <c r="E1278">
+        <v>0</v>
+      </c>
+      <c r="F1278">
+        <v>0</v>
+      </c>
+      <c r="G1278">
+        <v>0</v>
+      </c>
+      <c r="H1278">
+        <v>0</v>
+      </c>
+      <c r="I1278" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1279" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1279">
+        <v>0</v>
+      </c>
+      <c r="E1279">
+        <v>0</v>
+      </c>
+      <c r="F1279">
+        <v>0</v>
+      </c>
+      <c r="G1279">
+        <v>0</v>
+      </c>
+      <c r="H1279">
+        <v>0</v>
+      </c>
+      <c r="I1279" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1280" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1280">
+        <v>0</v>
+      </c>
+      <c r="E1280">
+        <v>0</v>
+      </c>
+      <c r="F1280">
+        <v>0</v>
+      </c>
+      <c r="G1280">
+        <v>0</v>
+      </c>
+      <c r="H1280">
+        <v>0</v>
+      </c>
+      <c r="I1280" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1281" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1281">
+        <v>0</v>
+      </c>
+      <c r="E1281">
+        <v>0</v>
+      </c>
+      <c r="F1281">
+        <v>0</v>
+      </c>
+      <c r="G1281">
+        <v>0</v>
+      </c>
+      <c r="H1281">
+        <v>0</v>
+      </c>
+      <c r="I1281" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1282" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1282">
+        <v>0</v>
+      </c>
+      <c r="E1282">
+        <v>0</v>
+      </c>
+      <c r="F1282">
+        <v>0</v>
+      </c>
+      <c r="G1282">
+        <v>0</v>
+      </c>
+      <c r="H1282">
+        <v>0</v>
+      </c>
+      <c r="I1282" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1283" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1283">
+        <v>0</v>
+      </c>
+      <c r="E1283">
+        <v>0</v>
+      </c>
+      <c r="F1283">
+        <v>0</v>
+      </c>
+      <c r="G1283">
+        <v>0</v>
+      </c>
+      <c r="H1283">
+        <v>0</v>
+      </c>
+      <c r="I1283" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1284" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1284">
+        <v>0</v>
+      </c>
+      <c r="E1284">
+        <v>0</v>
+      </c>
+      <c r="F1284">
+        <v>0</v>
+      </c>
+      <c r="G1284">
+        <v>0</v>
+      </c>
+      <c r="H1284">
+        <v>0</v>
+      </c>
+      <c r="I1284" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1285" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1285">
+        <v>1235</v>
+      </c>
+      <c r="E1285">
+        <v>10</v>
+      </c>
+      <c r="F1285">
+        <v>157.59</v>
+      </c>
+      <c r="G1285">
+        <v>0</v>
+      </c>
+      <c r="H1285">
+        <v>0</v>
+      </c>
+      <c r="I1285" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1286" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1286">
+        <v>925</v>
+      </c>
+      <c r="E1286">
+        <v>6</v>
+      </c>
+      <c r="F1286">
+        <v>93.6</v>
+      </c>
+      <c r="G1286">
+        <v>0</v>
+      </c>
+      <c r="H1286">
+        <v>0</v>
+      </c>
+      <c r="I1286" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1287" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1287">
+        <v>1119</v>
+      </c>
+      <c r="E1287">
+        <v>13</v>
+      </c>
+      <c r="F1287">
+        <v>204.52</v>
+      </c>
+      <c r="G1287">
+        <v>0</v>
+      </c>
+      <c r="H1287">
+        <v>0</v>
+      </c>
+      <c r="I1287" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1288" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1288">
+        <v>563</v>
+      </c>
+      <c r="E1288">
+        <v>4</v>
+      </c>
+      <c r="F1288">
+        <v>67.239999999999995</v>
+      </c>
+      <c r="G1288">
+        <v>0</v>
+      </c>
+      <c r="H1288">
+        <v>0</v>
+      </c>
+      <c r="I1288" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1289" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1289">
+        <v>0</v>
+      </c>
+      <c r="E1289">
+        <v>0</v>
+      </c>
+      <c r="F1289">
+        <v>0</v>
+      </c>
+      <c r="G1289">
+        <v>0</v>
+      </c>
+      <c r="H1289">
+        <v>0</v>
+      </c>
+      <c r="I1289" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1290" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1290">
+        <v>0</v>
+      </c>
+      <c r="E1290">
+        <v>0</v>
+      </c>
+      <c r="F1290">
+        <v>0</v>
+      </c>
+      <c r="G1290">
+        <v>0</v>
+      </c>
+      <c r="H1290">
+        <v>0</v>
+      </c>
+      <c r="I1290" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1291" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1291">
+        <v>0</v>
+      </c>
+      <c r="E1291">
+        <v>0</v>
+      </c>
+      <c r="F1291">
+        <v>0</v>
+      </c>
+      <c r="G1291">
+        <v>0</v>
+      </c>
+      <c r="H1291">
+        <v>0</v>
+      </c>
+      <c r="I1291" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1292" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1292">
+        <v>0</v>
+      </c>
+      <c r="E1292">
+        <v>0</v>
+      </c>
+      <c r="F1292">
+        <v>0</v>
+      </c>
+      <c r="G1292">
+        <v>0</v>
+      </c>
+      <c r="H1292">
+        <v>0</v>
+      </c>
+      <c r="I1292" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1293" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1293">
+        <v>0</v>
+      </c>
+      <c r="E1293">
+        <v>0</v>
+      </c>
+      <c r="F1293">
+        <v>0</v>
+      </c>
+      <c r="G1293">
+        <v>0</v>
+      </c>
+      <c r="H1293">
+        <v>0</v>
+      </c>
+      <c r="I1293" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1294" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1294">
+        <v>0</v>
+      </c>
+      <c r="E1294">
+        <v>0</v>
+      </c>
+      <c r="F1294">
+        <v>0</v>
+      </c>
+      <c r="G1294">
+        <v>0</v>
+      </c>
+      <c r="H1294">
+        <v>0</v>
+      </c>
+      <c r="I1294" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1295" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1295">
+        <v>0</v>
+      </c>
+      <c r="E1295">
+        <v>0</v>
+      </c>
+      <c r="F1295">
+        <v>0</v>
+      </c>
+      <c r="G1295">
+        <v>0</v>
+      </c>
+      <c r="H1295">
+        <v>0</v>
+      </c>
+      <c r="I1295" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1296" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1296">
+        <v>0</v>
+      </c>
+      <c r="E1296">
+        <v>0</v>
+      </c>
+      <c r="F1296">
+        <v>0</v>
+      </c>
+      <c r="G1296">
+        <v>0</v>
+      </c>
+      <c r="H1296">
+        <v>0</v>
+      </c>
+      <c r="I1296" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1297" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1297">
+        <v>0</v>
+      </c>
+      <c r="E1297">
+        <v>0</v>
+      </c>
+      <c r="F1297">
+        <v>0</v>
+      </c>
+      <c r="G1297">
+        <v>0</v>
+      </c>
+      <c r="H1297">
+        <v>0</v>
+      </c>
+      <c r="I1297" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1298" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1298">
+        <v>0</v>
+      </c>
+      <c r="E1298">
+        <v>0</v>
+      </c>
+      <c r="F1298">
+        <v>0</v>
+      </c>
+      <c r="G1298">
+        <v>0</v>
+      </c>
+      <c r="H1298">
+        <v>0</v>
+      </c>
+      <c r="I1298" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1299" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1299">
+        <v>0</v>
+      </c>
+      <c r="E1299">
+        <v>0</v>
+      </c>
+      <c r="F1299">
+        <v>0</v>
+      </c>
+      <c r="G1299">
+        <v>0</v>
+      </c>
+      <c r="H1299">
+        <v>0</v>
+      </c>
+      <c r="I1299" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1300" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1300">
+        <v>0</v>
+      </c>
+      <c r="E1300">
+        <v>0</v>
+      </c>
+      <c r="F1300">
+        <v>0</v>
+      </c>
+      <c r="G1300">
+        <v>0</v>
+      </c>
+      <c r="H1300">
+        <v>0</v>
+      </c>
+      <c r="I1300" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1301" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1301">
+        <v>0</v>
+      </c>
+      <c r="E1301">
+        <v>0</v>
+      </c>
+      <c r="F1301">
+        <v>0</v>
+      </c>
+      <c r="G1301">
+        <v>0</v>
+      </c>
+      <c r="H1301">
+        <v>0</v>
+      </c>
+      <c r="I1301" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1302" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1302">
+        <v>0</v>
+      </c>
+      <c r="E1302">
+        <v>0</v>
+      </c>
+      <c r="F1302">
+        <v>0</v>
+      </c>
+      <c r="G1302">
+        <v>0</v>
+      </c>
+      <c r="H1302">
+        <v>0</v>
+      </c>
+      <c r="I1302" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1303" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1303">
+        <v>316</v>
+      </c>
+      <c r="E1303">
+        <v>6</v>
+      </c>
+      <c r="F1303">
+        <v>78.45</v>
+      </c>
+      <c r="G1303">
+        <v>0</v>
+      </c>
+      <c r="H1303">
+        <v>0</v>
+      </c>
+      <c r="I1303" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1304" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1304">
+        <v>79</v>
+      </c>
+      <c r="E1304">
+        <v>3</v>
+      </c>
+      <c r="F1304">
+        <v>38.67</v>
+      </c>
+      <c r="G1304">
+        <v>0</v>
+      </c>
+      <c r="H1304">
+        <v>0</v>
+      </c>
+      <c r="I1304" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1305" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1305">
+        <v>0</v>
+      </c>
+      <c r="E1305">
+        <v>0</v>
+      </c>
+      <c r="F1305">
+        <v>0</v>
+      </c>
+      <c r="G1305">
+        <v>0</v>
+      </c>
+      <c r="H1305">
+        <v>0</v>
+      </c>
+      <c r="I1305" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1306" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1306">
+        <v>0</v>
+      </c>
+      <c r="E1306">
+        <v>0</v>
+      </c>
+      <c r="F1306">
+        <v>0</v>
+      </c>
+      <c r="G1306">
+        <v>0</v>
+      </c>
+      <c r="H1306">
+        <v>0</v>
+      </c>
+      <c r="I1306" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1307" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1307">
+        <v>0</v>
+      </c>
+      <c r="E1307">
+        <v>0</v>
+      </c>
+      <c r="F1307">
+        <v>0</v>
+      </c>
+      <c r="G1307">
+        <v>0</v>
+      </c>
+      <c r="H1307">
+        <v>0</v>
+      </c>
+      <c r="I1307" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1308" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1308">
+        <v>0</v>
+      </c>
+      <c r="E1308">
+        <v>0</v>
+      </c>
+      <c r="F1308">
+        <v>0</v>
+      </c>
+      <c r="G1308">
+        <v>0</v>
+      </c>
+      <c r="H1308">
+        <v>0</v>
+      </c>
+      <c r="I1308" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1309" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1309">
+        <v>0</v>
+      </c>
+      <c r="E1309">
+        <v>0</v>
+      </c>
+      <c r="F1309">
+        <v>0</v>
+      </c>
+      <c r="G1309">
+        <v>0</v>
+      </c>
+      <c r="H1309">
+        <v>0</v>
+      </c>
+      <c r="I1309" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1310" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1310">
+        <v>0</v>
+      </c>
+      <c r="E1310">
+        <v>0</v>
+      </c>
+      <c r="F1310">
+        <v>0</v>
+      </c>
+      <c r="G1310">
+        <v>0</v>
+      </c>
+      <c r="H1310">
+        <v>0</v>
+      </c>
+      <c r="I1310" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1311" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1311">
+        <v>0</v>
+      </c>
+      <c r="E1311">
+        <v>0</v>
+      </c>
+      <c r="F1311">
+        <v>0</v>
+      </c>
+      <c r="G1311">
+        <v>0</v>
+      </c>
+      <c r="H1311">
+        <v>0</v>
+      </c>
+      <c r="I1311" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1312" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1312">
+        <v>0</v>
+      </c>
+      <c r="E1312">
+        <v>0</v>
+      </c>
+      <c r="F1312">
+        <v>0</v>
+      </c>
+      <c r="G1312">
+        <v>0</v>
+      </c>
+      <c r="H1312">
+        <v>0</v>
+      </c>
+      <c r="I1312" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1313" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1313">
+        <v>0</v>
+      </c>
+      <c r="E1313">
+        <v>0</v>
+      </c>
+      <c r="F1313">
+        <v>0</v>
+      </c>
+      <c r="G1313">
+        <v>0</v>
+      </c>
+      <c r="H1313">
+        <v>0</v>
+      </c>
+      <c r="I1313" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1314" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1314">
+        <v>0</v>
+      </c>
+      <c r="E1314">
+        <v>0</v>
+      </c>
+      <c r="F1314">
+        <v>0</v>
+      </c>
+      <c r="G1314">
+        <v>0</v>
+      </c>
+      <c r="H1314">
+        <v>0</v>
+      </c>
+      <c r="I1314" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1315" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1315">
+        <v>0</v>
+      </c>
+      <c r="E1315">
+        <v>0</v>
+      </c>
+      <c r="F1315">
+        <v>0</v>
+      </c>
+      <c r="G1315">
+        <v>0</v>
+      </c>
+      <c r="H1315">
+        <v>0</v>
+      </c>
+      <c r="I1315" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1316" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1316">
+        <v>0</v>
+      </c>
+      <c r="E1316">
+        <v>0</v>
+      </c>
+      <c r="F1316">
+        <v>0</v>
+      </c>
+      <c r="G1316">
+        <v>0</v>
+      </c>
+      <c r="H1316">
+        <v>0</v>
+      </c>
+      <c r="I1316" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1317" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1317">
+        <v>0</v>
+      </c>
+      <c r="E1317">
+        <v>0</v>
+      </c>
+      <c r="F1317">
+        <v>0</v>
+      </c>
+      <c r="G1317">
+        <v>0</v>
+      </c>
+      <c r="H1317">
+        <v>0</v>
+      </c>
+      <c r="I1317" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1318" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1318">
+        <v>0</v>
+      </c>
+      <c r="E1318">
+        <v>0</v>
+      </c>
+      <c r="F1318">
+        <v>0</v>
+      </c>
+      <c r="G1318">
+        <v>0</v>
+      </c>
+      <c r="H1318">
+        <v>0</v>
+      </c>
+      <c r="I1318" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1319" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1319">
+        <v>0</v>
+      </c>
+      <c r="E1319">
+        <v>0</v>
+      </c>
+      <c r="F1319">
+        <v>0</v>
+      </c>
+      <c r="G1319">
+        <v>0</v>
+      </c>
+      <c r="H1319">
+        <v>0</v>
+      </c>
+      <c r="I1319" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1320" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1320">
+        <v>0</v>
+      </c>
+      <c r="E1320">
+        <v>0</v>
+      </c>
+      <c r="F1320">
+        <v>0</v>
+      </c>
+      <c r="G1320">
+        <v>0</v>
+      </c>
+      <c r="H1320">
+        <v>0</v>
+      </c>
+      <c r="I1320" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1321" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1321">
+        <v>0</v>
+      </c>
+      <c r="E1321">
+        <v>0</v>
+      </c>
+      <c r="F1321">
+        <v>0</v>
+      </c>
+      <c r="G1321">
+        <v>0</v>
+      </c>
+      <c r="H1321">
+        <v>0</v>
+      </c>
+      <c r="I1321" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1322" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1322">
+        <v>0</v>
+      </c>
+      <c r="E1322">
+        <v>0</v>
+      </c>
+      <c r="F1322">
+        <v>0</v>
+      </c>
+      <c r="G1322">
+        <v>0</v>
+      </c>
+      <c r="H1322">
+        <v>0</v>
+      </c>
+      <c r="I1322" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1323" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1323">
+        <v>0</v>
+      </c>
+      <c r="E1323">
+        <v>0</v>
+      </c>
+      <c r="F1323">
+        <v>0</v>
+      </c>
+      <c r="G1323">
+        <v>0</v>
+      </c>
+      <c r="H1323">
+        <v>0</v>
+      </c>
+      <c r="I1323" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1324" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1324">
+        <v>0</v>
+      </c>
+      <c r="E1324">
+        <v>0</v>
+      </c>
+      <c r="F1324">
+        <v>0</v>
+      </c>
+      <c r="G1324">
+        <v>0</v>
+      </c>
+      <c r="H1324">
+        <v>0</v>
+      </c>
+      <c r="I1324" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1325" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1325">
+        <v>0</v>
+      </c>
+      <c r="E1325">
+        <v>0</v>
+      </c>
+      <c r="F1325">
+        <v>0</v>
+      </c>
+      <c r="G1325">
+        <v>0</v>
+      </c>
+      <c r="H1325">
+        <v>0</v>
+      </c>
+      <c r="I1325" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1326" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1326">
+        <v>0</v>
+      </c>
+      <c r="E1326">
+        <v>0</v>
+      </c>
+      <c r="F1326">
+        <v>0</v>
+      </c>
+      <c r="G1326">
+        <v>0</v>
+      </c>
+      <c r="H1326">
+        <v>0</v>
+      </c>
+      <c r="I1326" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1327" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1327">
+        <v>0</v>
+      </c>
+      <c r="E1327">
+        <v>0</v>
+      </c>
+      <c r="F1327">
+        <v>0</v>
+      </c>
+      <c r="G1327">
+        <v>0</v>
+      </c>
+      <c r="H1327">
+        <v>0</v>
+      </c>
+      <c r="I1327" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1328" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1328">
+        <v>0</v>
+      </c>
+      <c r="E1328">
+        <v>0</v>
+      </c>
+      <c r="F1328">
+        <v>0</v>
+      </c>
+      <c r="G1328">
+        <v>0</v>
+      </c>
+      <c r="H1328">
+        <v>0</v>
+      </c>
+      <c r="I1328" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1329" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1329">
+        <v>0</v>
+      </c>
+      <c r="E1329">
+        <v>0</v>
+      </c>
+      <c r="F1329">
+        <v>0</v>
+      </c>
+      <c r="G1329">
+        <v>0</v>
+      </c>
+      <c r="H1329">
+        <v>0</v>
+      </c>
+      <c r="I1329" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1330" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1330">
+        <v>0</v>
+      </c>
+      <c r="E1330">
+        <v>0</v>
+      </c>
+      <c r="F1330">
+        <v>0</v>
+      </c>
+      <c r="G1330">
+        <v>0</v>
+      </c>
+      <c r="H1330">
+        <v>0</v>
+      </c>
+      <c r="I1330" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1331" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1331">
+        <v>0</v>
+      </c>
+      <c r="E1331">
+        <v>0</v>
+      </c>
+      <c r="F1331">
+        <v>0</v>
+      </c>
+      <c r="G1331">
+        <v>0</v>
+      </c>
+      <c r="H1331">
+        <v>0</v>
+      </c>
+      <c r="I1331" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1332" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1332">
+        <v>0</v>
+      </c>
+      <c r="E1332">
+        <v>0</v>
+      </c>
+      <c r="F1332">
+        <v>0</v>
+      </c>
+      <c r="G1332">
+        <v>0</v>
+      </c>
+      <c r="H1332">
+        <v>0</v>
+      </c>
+      <c r="I1332" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1333" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1333">
+        <v>0</v>
+      </c>
+      <c r="E1333">
+        <v>0</v>
+      </c>
+      <c r="F1333">
+        <v>0</v>
+      </c>
+      <c r="G1333">
+        <v>0</v>
+      </c>
+      <c r="H1333">
+        <v>0</v>
+      </c>
+      <c r="I1333" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1334" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1334">
+        <v>0</v>
+      </c>
+      <c r="E1334">
+        <v>0</v>
+      </c>
+      <c r="F1334">
+        <v>0</v>
+      </c>
+      <c r="G1334">
+        <v>0</v>
+      </c>
+      <c r="H1334">
+        <v>0</v>
+      </c>
+      <c r="I1334" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1335" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1335">
+        <v>0</v>
+      </c>
+      <c r="E1335">
+        <v>0</v>
+      </c>
+      <c r="F1335">
+        <v>0</v>
+      </c>
+      <c r="G1335">
+        <v>0</v>
+      </c>
+      <c r="H1335">
+        <v>0</v>
+      </c>
+      <c r="I1335" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1336" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1336">
+        <v>0</v>
+      </c>
+      <c r="E1336">
+        <v>0</v>
+      </c>
+      <c r="F1336">
+        <v>0</v>
+      </c>
+      <c r="G1336">
+        <v>0</v>
+      </c>
+      <c r="H1336">
+        <v>0</v>
+      </c>
+      <c r="I1336" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1337" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1337">
+        <v>0</v>
+      </c>
+      <c r="E1337">
+        <v>0</v>
+      </c>
+      <c r="F1337">
+        <v>0</v>
+      </c>
+      <c r="G1337">
+        <v>0</v>
+      </c>
+      <c r="H1337">
+        <v>0</v>
+      </c>
+      <c r="I1337" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1338" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1338">
+        <v>0</v>
+      </c>
+      <c r="E1338">
+        <v>0</v>
+      </c>
+      <c r="F1338">
+        <v>0</v>
+      </c>
+      <c r="G1338">
+        <v>0</v>
+      </c>
+      <c r="H1338">
+        <v>0</v>
+      </c>
+      <c r="I1338" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1339" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1339">
+        <v>0</v>
+      </c>
+      <c r="E1339">
+        <v>0</v>
+      </c>
+      <c r="F1339">
+        <v>0</v>
+      </c>
+      <c r="G1339">
+        <v>0</v>
+      </c>
+      <c r="H1339">
+        <v>0</v>
+      </c>
+      <c r="I1339" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1340" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1340">
+        <v>0</v>
+      </c>
+      <c r="E1340">
+        <v>0</v>
+      </c>
+      <c r="F1340">
+        <v>0</v>
+      </c>
+      <c r="G1340">
+        <v>0</v>
+      </c>
+      <c r="H1340">
+        <v>0</v>
+      </c>
+      <c r="I1340" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1341" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1341">
+        <v>0</v>
+      </c>
+      <c r="E1341">
+        <v>0</v>
+      </c>
+      <c r="F1341">
+        <v>0</v>
+      </c>
+      <c r="G1341">
+        <v>0</v>
+      </c>
+      <c r="H1341">
+        <v>0</v>
+      </c>
+      <c r="I1341" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1342" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1342">
+        <v>0</v>
+      </c>
+      <c r="E1342">
+        <v>0</v>
+      </c>
+      <c r="F1342">
+        <v>0</v>
+      </c>
+      <c r="G1342">
+        <v>0</v>
+      </c>
+      <c r="H1342">
+        <v>0</v>
+      </c>
+      <c r="I1342" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1343" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1343">
+        <v>0</v>
+      </c>
+      <c r="E1343">
+        <v>0</v>
+      </c>
+      <c r="F1343">
+        <v>0</v>
+      </c>
+      <c r="G1343">
+        <v>0</v>
+      </c>
+      <c r="H1343">
+        <v>0</v>
+      </c>
+      <c r="I1343" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1344" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1344">
+        <v>0</v>
+      </c>
+      <c r="E1344">
+        <v>0</v>
+      </c>
+      <c r="F1344">
+        <v>0</v>
+      </c>
+      <c r="G1344">
+        <v>0</v>
+      </c>
+      <c r="H1344">
+        <v>0</v>
+      </c>
+      <c r="I1344" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1345" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1345">
+        <v>0</v>
+      </c>
+      <c r="E1345">
+        <v>0</v>
+      </c>
+      <c r="F1345">
+        <v>0</v>
+      </c>
+      <c r="G1345">
+        <v>0</v>
+      </c>
+      <c r="H1345">
+        <v>0</v>
+      </c>
+      <c r="I1345" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1346" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1346">
+        <v>542</v>
+      </c>
+      <c r="E1346">
+        <v>16</v>
+      </c>
+      <c r="F1346">
+        <v>137.59</v>
+      </c>
+      <c r="G1346">
+        <v>0</v>
+      </c>
+      <c r="H1346">
+        <v>0</v>
+      </c>
+      <c r="I1346" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1347" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1347">
+        <v>1051</v>
+      </c>
+      <c r="E1347">
+        <v>34</v>
+      </c>
+      <c r="F1347">
+        <v>344.04</v>
+      </c>
+      <c r="G1347">
+        <v>0</v>
+      </c>
+      <c r="H1347">
+        <v>0</v>
+      </c>
+      <c r="I1347" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1348" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1348">
+        <v>0</v>
+      </c>
+      <c r="E1348">
+        <v>0</v>
+      </c>
+      <c r="F1348">
+        <v>0</v>
+      </c>
+      <c r="G1348">
+        <v>0</v>
+      </c>
+      <c r="H1348">
+        <v>0</v>
+      </c>
+      <c r="I1348" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1349" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1349">
+        <v>0</v>
+      </c>
+      <c r="E1349">
+        <v>0</v>
+      </c>
+      <c r="F1349">
+        <v>0</v>
+      </c>
+      <c r="G1349">
+        <v>0</v>
+      </c>
+      <c r="H1349">
+        <v>0</v>
+      </c>
+      <c r="I1349" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1350" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1350">
+        <v>0</v>
+      </c>
+      <c r="E1350">
+        <v>0</v>
+      </c>
+      <c r="F1350">
+        <v>0</v>
+      </c>
+      <c r="G1350">
+        <v>0</v>
+      </c>
+      <c r="H1350">
+        <v>0</v>
+      </c>
+      <c r="I1350" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1351" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1351">
+        <v>0</v>
+      </c>
+      <c r="E1351">
+        <v>0</v>
+      </c>
+      <c r="F1351">
+        <v>0</v>
+      </c>
+      <c r="G1351">
+        <v>0</v>
+      </c>
+      <c r="H1351">
+        <v>0</v>
+      </c>
+      <c r="I1351" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1352" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1352">
+        <v>0</v>
+      </c>
+      <c r="E1352">
+        <v>0</v>
+      </c>
+      <c r="F1352">
+        <v>0</v>
+      </c>
+      <c r="G1352">
+        <v>0</v>
+      </c>
+      <c r="H1352">
+        <v>0</v>
+      </c>
+      <c r="I1352" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1353" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1353">
+        <v>0</v>
+      </c>
+      <c r="E1353">
+        <v>0</v>
+      </c>
+      <c r="F1353">
+        <v>0</v>
+      </c>
+      <c r="G1353">
+        <v>0</v>
+      </c>
+      <c r="H1353">
+        <v>0</v>
+      </c>
+      <c r="I1353" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1354" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1354">
+        <v>0</v>
+      </c>
+      <c r="E1354">
+        <v>0</v>
+      </c>
+      <c r="F1354">
+        <v>0</v>
+      </c>
+      <c r="G1354">
+        <v>0</v>
+      </c>
+      <c r="H1354">
+        <v>0</v>
+      </c>
+      <c r="I1354" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1355" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1355">
+        <v>0</v>
+      </c>
+      <c r="E1355">
+        <v>0</v>
+      </c>
+      <c r="F1355">
+        <v>0</v>
+      </c>
+      <c r="G1355">
+        <v>0</v>
+      </c>
+      <c r="H1355">
+        <v>0</v>
+      </c>
+      <c r="I1355" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1356" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1356">
+        <v>0</v>
+      </c>
+      <c r="E1356">
+        <v>0</v>
+      </c>
+      <c r="F1356">
+        <v>0</v>
+      </c>
+      <c r="G1356">
+        <v>0</v>
+      </c>
+      <c r="H1356">
+        <v>0</v>
+      </c>
+      <c r="I1356" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1357" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1357">
+        <v>0</v>
+      </c>
+      <c r="E1357">
+        <v>0</v>
+      </c>
+      <c r="F1357">
+        <v>0</v>
+      </c>
+      <c r="G1357">
+        <v>0</v>
+      </c>
+      <c r="H1357">
+        <v>0</v>
+      </c>
+      <c r="I1357" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1358" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1358">
+        <v>0</v>
+      </c>
+      <c r="E1358">
+        <v>0</v>
+      </c>
+      <c r="F1358">
+        <v>0</v>
+      </c>
+      <c r="G1358">
+        <v>0</v>
+      </c>
+      <c r="H1358">
+        <v>0</v>
+      </c>
+      <c r="I1358" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1359" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1359">
+        <v>0</v>
+      </c>
+      <c r="E1359">
+        <v>0</v>
+      </c>
+      <c r="F1359">
+        <v>0</v>
+      </c>
+      <c r="G1359">
+        <v>0</v>
+      </c>
+      <c r="H1359">
+        <v>0</v>
+      </c>
+      <c r="I1359" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1360" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1360">
+        <v>0</v>
+      </c>
+      <c r="E1360">
+        <v>0</v>
+      </c>
+      <c r="F1360">
+        <v>0</v>
+      </c>
+      <c r="G1360">
+        <v>0</v>
+      </c>
+      <c r="H1360">
+        <v>0</v>
+      </c>
+      <c r="I1360" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1361" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1361">
+        <v>0</v>
+      </c>
+      <c r="E1361">
+        <v>0</v>
+      </c>
+      <c r="F1361">
+        <v>0</v>
+      </c>
+      <c r="G1361">
+        <v>0</v>
+      </c>
+      <c r="H1361">
+        <v>0</v>
+      </c>
+      <c r="I1361" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1362" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1362">
+        <v>0</v>
+      </c>
+      <c r="E1362">
+        <v>0</v>
+      </c>
+      <c r="F1362">
+        <v>0</v>
+      </c>
+      <c r="G1362">
+        <v>0</v>
+      </c>
+      <c r="H1362">
+        <v>0</v>
+      </c>
+      <c r="I1362" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1363" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1363">
+        <v>0</v>
+      </c>
+      <c r="E1363">
+        <v>0</v>
+      </c>
+      <c r="F1363">
+        <v>0</v>
+      </c>
+      <c r="G1363">
+        <v>0</v>
+      </c>
+      <c r="H1363">
+        <v>0</v>
+      </c>
+      <c r="I1363" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1364" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1364">
+        <v>0</v>
+      </c>
+      <c r="E1364">
+        <v>0</v>
+      </c>
+      <c r="F1364">
+        <v>0</v>
+      </c>
+      <c r="G1364">
+        <v>0</v>
+      </c>
+      <c r="H1364">
+        <v>0</v>
+      </c>
+      <c r="I1364" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1365" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1365">
+        <v>0</v>
+      </c>
+      <c r="E1365">
+        <v>0</v>
+      </c>
+      <c r="F1365">
+        <v>0</v>
+      </c>
+      <c r="G1365">
+        <v>0</v>
+      </c>
+      <c r="H1365">
+        <v>0</v>
+      </c>
+      <c r="I1365" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1366" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1366">
+        <v>0</v>
+      </c>
+      <c r="E1366">
+        <v>0</v>
+      </c>
+      <c r="F1366">
+        <v>0</v>
+      </c>
+      <c r="G1366">
+        <v>0</v>
+      </c>
+      <c r="H1366">
+        <v>0</v>
+      </c>
+      <c r="I1366" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1367" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1367">
+        <v>0</v>
+      </c>
+      <c r="E1367">
+        <v>0</v>
+      </c>
+      <c r="F1367">
+        <v>0</v>
+      </c>
+      <c r="G1367">
+        <v>0</v>
+      </c>
+      <c r="H1367">
+        <v>0</v>
+      </c>
+      <c r="I1367" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1368" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1368">
+        <v>0</v>
+      </c>
+      <c r="E1368">
+        <v>0</v>
+      </c>
+      <c r="F1368">
+        <v>0</v>
+      </c>
+      <c r="G1368">
+        <v>0</v>
+      </c>
+      <c r="H1368">
+        <v>0</v>
+      </c>
+      <c r="I1368" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1369" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1369">
+        <v>0</v>
+      </c>
+      <c r="E1369">
+        <v>0</v>
+      </c>
+      <c r="F1369">
+        <v>0</v>
+      </c>
+      <c r="G1369">
+        <v>0</v>
+      </c>
+      <c r="H1369">
+        <v>0</v>
+      </c>
+      <c r="I1369" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1370" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1370">
+        <v>0</v>
+      </c>
+      <c r="E1370">
+        <v>0</v>
+      </c>
+      <c r="F1370">
+        <v>0</v>
+      </c>
+      <c r="G1370">
+        <v>0</v>
+      </c>
+      <c r="H1370">
+        <v>0</v>
+      </c>
+      <c r="I1370" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1371" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1371">
+        <v>0</v>
+      </c>
+      <c r="E1371">
+        <v>0</v>
+      </c>
+      <c r="F1371">
+        <v>0</v>
+      </c>
+      <c r="G1371">
+        <v>0</v>
+      </c>
+      <c r="H1371">
+        <v>0</v>
+      </c>
+      <c r="I1371" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1372" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1372">
+        <v>0</v>
+      </c>
+      <c r="E1372">
+        <v>0</v>
+      </c>
+      <c r="F1372">
+        <v>0</v>
+      </c>
+      <c r="G1372">
+        <v>0</v>
+      </c>
+      <c r="H1372">
+        <v>0</v>
+      </c>
+      <c r="I1372" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1373" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1373">
+        <v>0</v>
+      </c>
+      <c r="E1373">
+        <v>0</v>
+      </c>
+      <c r="F1373">
+        <v>0</v>
+      </c>
+      <c r="G1373">
+        <v>0</v>
+      </c>
+      <c r="H1373">
+        <v>0</v>
+      </c>
+      <c r="I1373" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1374" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1374">
+        <v>0</v>
+      </c>
+      <c r="E1374">
+        <v>0</v>
+      </c>
+      <c r="F1374">
+        <v>0</v>
+      </c>
+      <c r="G1374">
+        <v>0</v>
+      </c>
+      <c r="H1374">
+        <v>0</v>
+      </c>
+      <c r="I1374" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1375" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1375">
+        <v>0</v>
+      </c>
+      <c r="E1375">
+        <v>0</v>
+      </c>
+      <c r="F1375">
+        <v>0</v>
+      </c>
+      <c r="G1375">
+        <v>0</v>
+      </c>
+      <c r="H1375">
+        <v>0</v>
+      </c>
+      <c r="I1375" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1376" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1376">
+        <v>1333</v>
+      </c>
+      <c r="E1376">
+        <v>23</v>
+      </c>
+      <c r="F1376">
+        <v>101.09</v>
+      </c>
+      <c r="G1376">
+        <v>0</v>
+      </c>
+      <c r="H1376">
+        <v>0</v>
+      </c>
+      <c r="I1376" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1377" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1377">
+        <v>1150</v>
+      </c>
+      <c r="E1377">
+        <v>5</v>
+      </c>
+      <c r="F1377">
+        <v>22.14</v>
+      </c>
+      <c r="G1377">
+        <v>0</v>
+      </c>
+      <c r="H1377">
+        <v>0</v>
+      </c>
+      <c r="I1377" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1378" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1378">
+        <v>1506</v>
+      </c>
+      <c r="E1378">
+        <v>8</v>
+      </c>
+      <c r="F1378">
+        <v>36.229999999999997</v>
+      </c>
+      <c r="G1378">
+        <v>0</v>
+      </c>
+      <c r="H1378">
+        <v>0</v>
+      </c>
+      <c r="I1378" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1379" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1379">
+        <v>2019</v>
+      </c>
+      <c r="E1379">
+        <v>17</v>
+      </c>
+      <c r="F1379">
+        <v>80.75</v>
+      </c>
+      <c r="G1379">
+        <v>0</v>
+      </c>
+      <c r="H1379">
+        <v>0</v>
+      </c>
+      <c r="I1379" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1380" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1380">
+        <v>812</v>
+      </c>
+      <c r="E1380">
+        <v>11</v>
+      </c>
+      <c r="F1380">
+        <v>48</v>
+      </c>
+      <c r="G1380">
+        <v>4150.84</v>
+      </c>
+      <c r="H1380">
+        <v>2</v>
+      </c>
+      <c r="I1380" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1381" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1381">
+        <v>967</v>
+      </c>
+      <c r="E1381">
+        <v>8</v>
+      </c>
+      <c r="F1381">
+        <v>41.17</v>
+      </c>
+      <c r="G1381">
+        <v>0</v>
+      </c>
+      <c r="H1381">
+        <v>0</v>
+      </c>
+      <c r="I1381" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1382" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1382">
+        <v>969</v>
+      </c>
+      <c r="E1382">
+        <v>14</v>
+      </c>
+      <c r="F1382">
+        <v>53.63</v>
+      </c>
+      <c r="G1382">
+        <v>0</v>
+      </c>
+      <c r="H1382">
+        <v>0</v>
+      </c>
+      <c r="I1382" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1383" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1383">
+        <v>2000</v>
+      </c>
+      <c r="E1383">
+        <v>43</v>
+      </c>
+      <c r="F1383">
+        <v>560.57000000000005</v>
+      </c>
+      <c r="G1383">
+        <v>4913.5600000000004</v>
+      </c>
+      <c r="H1383">
+        <v>2</v>
+      </c>
+      <c r="I1383" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1384" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1384">
+        <v>1592</v>
+      </c>
+      <c r="E1384">
+        <v>40</v>
+      </c>
+      <c r="F1384">
+        <v>582.05999999999995</v>
+      </c>
+      <c r="G1384">
+        <v>0</v>
+      </c>
+      <c r="H1384">
+        <v>0</v>
+      </c>
+      <c r="I1384" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1385" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1385">
+        <v>2010</v>
+      </c>
+      <c r="E1385">
+        <v>50</v>
+      </c>
+      <c r="F1385">
+        <v>592.13</v>
+      </c>
+      <c r="G1385">
+        <v>0</v>
+      </c>
+      <c r="H1385">
+        <v>0</v>
+      </c>
+      <c r="I1385" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1386" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1386">
+        <v>1742</v>
+      </c>
+      <c r="E1386">
+        <v>62</v>
+      </c>
+      <c r="F1386">
+        <v>725.01</v>
+      </c>
+      <c r="G1386">
+        <v>2456.7800000000002</v>
+      </c>
+      <c r="H1386">
+        <v>1</v>
+      </c>
+      <c r="I1386" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1387" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1387">
+        <v>2060</v>
+      </c>
+      <c r="E1387">
+        <v>52</v>
+      </c>
+      <c r="F1387">
+        <v>456.43</v>
+      </c>
+      <c r="G1387">
+        <v>2456.7800000000002</v>
+      </c>
+      <c r="H1387">
+        <v>1</v>
+      </c>
+      <c r="I1387" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1388" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1388">
+        <v>2358</v>
+      </c>
+      <c r="E1388">
+        <v>69</v>
+      </c>
+      <c r="F1388">
+        <v>795.38</v>
+      </c>
+      <c r="G1388">
+        <v>7878.81</v>
+      </c>
+      <c r="H1388">
+        <v>3</v>
+      </c>
+      <c r="I1388" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1389" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1389">
+        <v>2563</v>
+      </c>
+      <c r="E1389">
+        <v>57</v>
+      </c>
+      <c r="F1389">
+        <v>676.67</v>
+      </c>
+      <c r="G1389">
+        <v>0</v>
+      </c>
+      <c r="H1389">
+        <v>0</v>
+      </c>
+      <c r="I1389" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1390" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1390">
+        <v>0</v>
+      </c>
+      <c r="E1390">
+        <v>0</v>
+      </c>
+      <c r="F1390">
+        <v>0</v>
+      </c>
+      <c r="G1390">
+        <v>0</v>
+      </c>
+      <c r="H1390">
+        <v>0</v>
+      </c>
+      <c r="I1390" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1391" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1391">
+        <v>0</v>
+      </c>
+      <c r="E1391">
+        <v>0</v>
+      </c>
+      <c r="F1391">
+        <v>0</v>
+      </c>
+      <c r="G1391">
+        <v>0</v>
+      </c>
+      <c r="H1391">
+        <v>0</v>
+      </c>
+      <c r="I1391" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1392" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1392">
+        <v>0</v>
+      </c>
+      <c r="E1392">
+        <v>0</v>
+      </c>
+      <c r="F1392">
+        <v>0</v>
+      </c>
+      <c r="G1392">
+        <v>0</v>
+      </c>
+      <c r="H1392">
+        <v>0</v>
+      </c>
+      <c r="I1392" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1393" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1393">
+        <v>0</v>
+      </c>
+      <c r="E1393">
+        <v>0</v>
+      </c>
+      <c r="F1393">
+        <v>0</v>
+      </c>
+      <c r="G1393">
+        <v>0</v>
+      </c>
+      <c r="H1393">
+        <v>0</v>
+      </c>
+      <c r="I1393" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1394" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1394">
+        <v>0</v>
+      </c>
+      <c r="E1394">
+        <v>0</v>
+      </c>
+      <c r="F1394">
+        <v>0</v>
+      </c>
+      <c r="G1394">
+        <v>0</v>
+      </c>
+      <c r="H1394">
+        <v>0</v>
+      </c>
+      <c r="I1394" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1395" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1395">
+        <v>0</v>
+      </c>
+      <c r="E1395">
+        <v>0</v>
+      </c>
+      <c r="F1395">
+        <v>0</v>
+      </c>
+      <c r="G1395">
+        <v>0</v>
+      </c>
+      <c r="H1395">
+        <v>0</v>
+      </c>
+      <c r="I1395" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1396" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1396">
+        <v>0</v>
+      </c>
+      <c r="E1396">
+        <v>0</v>
+      </c>
+      <c r="F1396">
+        <v>0</v>
+      </c>
+      <c r="G1396">
+        <v>0</v>
+      </c>
+      <c r="H1396">
+        <v>0</v>
+      </c>
+      <c r="I1396" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1397" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1397">
+        <v>0</v>
+      </c>
+      <c r="E1397">
+        <v>0</v>
+      </c>
+      <c r="F1397">
+        <v>0</v>
+      </c>
+      <c r="G1397">
+        <v>0</v>
+      </c>
+      <c r="H1397">
+        <v>0</v>
+      </c>
+      <c r="I1397" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1398" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1398">
+        <v>0</v>
+      </c>
+      <c r="E1398">
+        <v>0</v>
+      </c>
+      <c r="F1398">
+        <v>0</v>
+      </c>
+      <c r="G1398">
+        <v>0</v>
+      </c>
+      <c r="H1398">
+        <v>0</v>
+      </c>
+      <c r="I1398" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1399" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1399">
+        <v>0</v>
+      </c>
+      <c r="E1399">
+        <v>0</v>
+      </c>
+      <c r="F1399">
+        <v>0</v>
+      </c>
+      <c r="G1399">
+        <v>0</v>
+      </c>
+      <c r="H1399">
+        <v>0</v>
+      </c>
+      <c r="I1399" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1400" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1400">
+        <v>0</v>
+      </c>
+      <c r="E1400">
+        <v>0</v>
+      </c>
+      <c r="F1400">
+        <v>0</v>
+      </c>
+      <c r="G1400">
+        <v>0</v>
+      </c>
+      <c r="H1400">
+        <v>0</v>
+      </c>
+      <c r="I1400" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1401" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1401">
+        <v>0</v>
+      </c>
+      <c r="E1401">
+        <v>0</v>
+      </c>
+      <c r="F1401">
+        <v>0</v>
+      </c>
+      <c r="G1401">
+        <v>0</v>
+      </c>
+      <c r="H1401">
+        <v>0</v>
+      </c>
+      <c r="I1401" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1402" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1402">
+        <v>0</v>
+      </c>
+      <c r="E1402">
+        <v>0</v>
+      </c>
+      <c r="F1402">
+        <v>0</v>
+      </c>
+      <c r="G1402">
+        <v>0</v>
+      </c>
+      <c r="H1402">
+        <v>0</v>
+      </c>
+      <c r="I1402" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1403" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1403">
+        <v>0</v>
+      </c>
+      <c r="E1403">
+        <v>0</v>
+      </c>
+      <c r="F1403">
+        <v>0</v>
+      </c>
+      <c r="G1403">
+        <v>0</v>
+      </c>
+      <c r="H1403">
+        <v>0</v>
+      </c>
+      <c r="I1403" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1404" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1404">
+        <v>0</v>
+      </c>
+      <c r="E1404">
+        <v>0</v>
+      </c>
+      <c r="F1404">
+        <v>0</v>
+      </c>
+      <c r="G1404">
+        <v>0</v>
+      </c>
+      <c r="H1404">
+        <v>0</v>
+      </c>
+      <c r="I1404" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1405" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1405">
+        <v>0</v>
+      </c>
+      <c r="E1405">
+        <v>0</v>
+      </c>
+      <c r="F1405">
+        <v>0</v>
+      </c>
+      <c r="G1405">
+        <v>0</v>
+      </c>
+      <c r="H1405">
+        <v>0</v>
+      </c>
+      <c r="I1405" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1406" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1406">
+        <v>0</v>
+      </c>
+      <c r="E1406">
+        <v>0</v>
+      </c>
+      <c r="F1406">
+        <v>0</v>
+      </c>
+      <c r="G1406">
+        <v>0</v>
+      </c>
+      <c r="H1406">
+        <v>0</v>
+      </c>
+      <c r="I1406" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1407" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1407">
+        <v>177</v>
+      </c>
+      <c r="E1407">
+        <v>12</v>
+      </c>
+      <c r="F1407">
+        <v>129.54</v>
+      </c>
+      <c r="G1407">
+        <v>0</v>
+      </c>
+      <c r="H1407">
+        <v>0</v>
+      </c>
+      <c r="I1407" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1408" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1408">
+        <v>301</v>
+      </c>
+      <c r="E1408">
+        <v>12</v>
+      </c>
+      <c r="F1408">
+        <v>128.19</v>
+      </c>
+      <c r="G1408">
+        <v>0</v>
+      </c>
+      <c r="H1408">
+        <v>0</v>
+      </c>
+      <c r="I1408" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1409" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1409">
+        <v>1288</v>
+      </c>
+      <c r="E1409">
+        <v>50</v>
+      </c>
+      <c r="F1409">
+        <v>282.39999999999998</v>
+      </c>
+      <c r="G1409">
+        <v>0</v>
+      </c>
+      <c r="H1409">
+        <v>0</v>
+      </c>
+      <c r="I1409" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1410" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1410">
+        <v>679</v>
+      </c>
+      <c r="E1410">
+        <v>23</v>
+      </c>
+      <c r="F1410">
+        <v>151.66999999999999</v>
+      </c>
+      <c r="G1410">
+        <v>0</v>
+      </c>
+      <c r="H1410">
+        <v>0</v>
+      </c>
+      <c r="I1410" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1411" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1411">
+        <v>270</v>
+      </c>
+      <c r="E1411">
+        <v>11</v>
+      </c>
+      <c r="F1411">
+        <v>61</v>
+      </c>
+      <c r="G1411">
+        <v>0</v>
+      </c>
+      <c r="H1411">
+        <v>0</v>
+      </c>
+      <c r="I1411" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1412" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1412">
+        <v>111</v>
+      </c>
+      <c r="E1412">
+        <v>10</v>
+      </c>
+      <c r="F1412">
+        <v>45.85</v>
+      </c>
+      <c r="G1412">
+        <v>0</v>
+      </c>
+      <c r="H1412">
+        <v>0</v>
+      </c>
+      <c r="I1412" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1413" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1413">
+        <v>210</v>
+      </c>
+      <c r="E1413">
+        <v>13</v>
+      </c>
+      <c r="F1413">
+        <v>51.83</v>
+      </c>
+      <c r="G1413">
+        <v>0</v>
+      </c>
+      <c r="H1413">
+        <v>0</v>
+      </c>
+      <c r="I1413" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1414" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1414">
+        <v>245</v>
+      </c>
+      <c r="E1414">
+        <v>16</v>
+      </c>
+      <c r="F1414">
+        <v>85.66</v>
+      </c>
+      <c r="G1414">
+        <v>0</v>
+      </c>
+      <c r="H1414">
+        <v>0</v>
+      </c>
+      <c r="I1414" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1415" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1415">
+        <v>839</v>
+      </c>
+      <c r="E1415">
+        <v>44</v>
+      </c>
+      <c r="F1415">
+        <v>212.3</v>
+      </c>
+      <c r="G1415">
+        <v>3520.96</v>
+      </c>
+      <c r="H1415">
+        <v>2</v>
+      </c>
+      <c r="I1415" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1416" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1416">
+        <v>504</v>
+      </c>
+      <c r="E1416">
+        <v>26</v>
+      </c>
+      <c r="F1416">
+        <v>121.85</v>
+      </c>
+      <c r="G1416">
+        <v>0</v>
+      </c>
+      <c r="H1416">
+        <v>0</v>
+      </c>
+      <c r="I1416" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1417" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1417">
+        <v>562</v>
+      </c>
+      <c r="E1417">
+        <v>34</v>
+      </c>
+      <c r="F1417">
+        <v>133.79</v>
+      </c>
+      <c r="G1417">
+        <v>0</v>
+      </c>
+      <c r="H1417">
+        <v>0</v>
+      </c>
+      <c r="I1417" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1418" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1418">
+        <v>0</v>
+      </c>
+      <c r="E1418">
+        <v>0</v>
+      </c>
+      <c r="F1418">
+        <v>0</v>
+      </c>
+      <c r="G1418">
+        <v>0</v>
+      </c>
+      <c r="H1418">
+        <v>0</v>
+      </c>
+      <c r="I1418" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1419" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1419">
+        <v>0</v>
+      </c>
+      <c r="E1419">
+        <v>0</v>
+      </c>
+      <c r="F1419">
+        <v>0</v>
+      </c>
+      <c r="G1419">
+        <v>0</v>
+      </c>
+      <c r="H1419">
+        <v>0</v>
+      </c>
+      <c r="I1419" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1420" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1420">
+        <v>0</v>
+      </c>
+      <c r="E1420">
+        <v>0</v>
+      </c>
+      <c r="F1420">
+        <v>0</v>
+      </c>
+      <c r="G1420">
+        <v>0</v>
+      </c>
+      <c r="H1420">
+        <v>0</v>
+      </c>
+      <c r="I1420" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1421" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1421" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1421">
+        <v>0</v>
+      </c>
+      <c r="E1421">
+        <v>0</v>
+      </c>
+      <c r="F1421">
+        <v>0</v>
+      </c>
+      <c r="G1421">
+        <v>0</v>
+      </c>
+      <c r="H1421">
+        <v>0</v>
+      </c>
+      <c r="I1421" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1422" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1422" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1422">
+        <v>0</v>
+      </c>
+      <c r="E1422">
+        <v>0</v>
+      </c>
+      <c r="F1422">
+        <v>0</v>
+      </c>
+      <c r="G1422">
+        <v>0</v>
+      </c>
+      <c r="H1422">
+        <v>0</v>
+      </c>
+      <c r="I1422" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1423" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1423">
+        <v>0</v>
+      </c>
+      <c r="E1423">
+        <v>0</v>
+      </c>
+      <c r="F1423">
+        <v>0</v>
+      </c>
+      <c r="G1423">
+        <v>0</v>
+      </c>
+      <c r="H1423">
+        <v>0</v>
+      </c>
+      <c r="I1423" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1424" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1424">
+        <v>0</v>
+      </c>
+      <c r="E1424">
+        <v>0</v>
+      </c>
+      <c r="F1424">
+        <v>0</v>
+      </c>
+      <c r="G1424">
+        <v>0</v>
+      </c>
+      <c r="H1424">
+        <v>0</v>
+      </c>
+      <c r="I1424" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1425" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1425">
+        <v>0</v>
+      </c>
+      <c r="E1425">
+        <v>0</v>
+      </c>
+      <c r="F1425">
+        <v>0</v>
+      </c>
+      <c r="G1425">
+        <v>0</v>
+      </c>
+      <c r="H1425">
+        <v>0</v>
+      </c>
+      <c r="I1425" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1426" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1426">
+        <v>0</v>
+      </c>
+      <c r="E1426">
+        <v>0</v>
+      </c>
+      <c r="F1426">
+        <v>0</v>
+      </c>
+      <c r="G1426">
+        <v>0</v>
+      </c>
+      <c r="H1426">
+        <v>0</v>
+      </c>
+      <c r="I1426" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1427" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1427">
+        <v>0</v>
+      </c>
+      <c r="E1427">
+        <v>0</v>
+      </c>
+      <c r="F1427">
+        <v>0</v>
+      </c>
+      <c r="G1427">
+        <v>0</v>
+      </c>
+      <c r="H1427">
+        <v>0</v>
+      </c>
+      <c r="I1427" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1428" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1428">
+        <v>0</v>
+      </c>
+      <c r="E1428">
+        <v>0</v>
+      </c>
+      <c r="F1428">
+        <v>0</v>
+      </c>
+      <c r="G1428">
+        <v>0</v>
+      </c>
+      <c r="H1428">
+        <v>0</v>
+      </c>
+      <c r="I1428" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1429" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1429">
+        <v>0</v>
+      </c>
+      <c r="E1429">
+        <v>0</v>
+      </c>
+      <c r="F1429">
+        <v>0</v>
+      </c>
+      <c r="G1429">
+        <v>0</v>
+      </c>
+      <c r="H1429">
+        <v>0</v>
+      </c>
+      <c r="I1429" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1430" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1430">
+        <v>0</v>
+      </c>
+      <c r="E1430">
+        <v>0</v>
+      </c>
+      <c r="F1430">
+        <v>0</v>
+      </c>
+      <c r="G1430">
+        <v>0</v>
+      </c>
+      <c r="H1430">
+        <v>0</v>
+      </c>
+      <c r="I1430" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1431" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1431">
+        <v>0</v>
+      </c>
+      <c r="E1431">
+        <v>0</v>
+      </c>
+      <c r="F1431">
+        <v>0</v>
+      </c>
+      <c r="G1431">
+        <v>0</v>
+      </c>
+      <c r="H1431">
+        <v>0</v>
+      </c>
+      <c r="I1431" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1432" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1432">
+        <v>855</v>
+      </c>
+      <c r="E1432">
+        <v>19</v>
+      </c>
+      <c r="F1432">
+        <v>184.06</v>
+      </c>
+      <c r="G1432">
+        <v>0</v>
+      </c>
+      <c r="H1432">
+        <v>0</v>
+      </c>
+      <c r="I1432" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1433" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1433">
+        <v>480</v>
+      </c>
+      <c r="E1433">
+        <v>10</v>
+      </c>
+      <c r="F1433">
+        <v>66.33</v>
+      </c>
+      <c r="G1433">
+        <v>1609.32</v>
+      </c>
+      <c r="H1433">
+        <v>1</v>
+      </c>
+      <c r="I1433" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1434" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1434">
+        <v>419</v>
+      </c>
+      <c r="E1434">
+        <v>8</v>
+      </c>
+      <c r="F1434">
+        <v>77.849999999999994</v>
+      </c>
+      <c r="G1434">
+        <v>0</v>
+      </c>
+      <c r="H1434">
+        <v>0</v>
+      </c>
+      <c r="I1434" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1435" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1435">
+        <v>194</v>
+      </c>
+      <c r="E1435">
+        <v>6</v>
+      </c>
+      <c r="F1435">
+        <v>32.36</v>
+      </c>
+      <c r="G1435">
+        <v>0</v>
+      </c>
+      <c r="H1435">
+        <v>0</v>
+      </c>
+      <c r="I1435" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1436" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1436" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1436">
+        <v>178</v>
+      </c>
+      <c r="E1436">
+        <v>5</v>
+      </c>
+      <c r="F1436">
+        <v>36.21</v>
+      </c>
+      <c r="G1436">
+        <v>0</v>
+      </c>
+      <c r="H1436">
+        <v>0</v>
+      </c>
+      <c r="I1436" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1437" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1437" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1437">
+        <v>173</v>
+      </c>
+      <c r="E1437">
+        <v>6</v>
+      </c>
+      <c r="F1437">
+        <v>41.23</v>
+      </c>
+      <c r="G1437">
+        <v>0</v>
+      </c>
+      <c r="H1437">
+        <v>0</v>
+      </c>
+      <c r="I1437" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1438" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1438" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1438">
+        <v>241</v>
+      </c>
+      <c r="E1438">
+        <v>4</v>
+      </c>
+      <c r="F1438">
+        <v>17.78</v>
+      </c>
+      <c r="G1438">
+        <v>0</v>
+      </c>
+      <c r="H1438">
+        <v>0</v>
+      </c>
+      <c r="I1438" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1439" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1439" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1439">
+        <v>0</v>
+      </c>
+      <c r="E1439">
+        <v>0</v>
+      </c>
+      <c r="F1439">
+        <v>0</v>
+      </c>
+      <c r="G1439">
+        <v>0</v>
+      </c>
+      <c r="H1439">
+        <v>0</v>
+      </c>
+      <c r="I1439" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1440" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1440" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1440">
+        <v>0</v>
+      </c>
+      <c r="E1440">
+        <v>0</v>
+      </c>
+      <c r="F1440">
+        <v>0</v>
+      </c>
+      <c r="G1440">
+        <v>0</v>
+      </c>
+      <c r="H1440">
+        <v>0</v>
+      </c>
+      <c r="I1440" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1441" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1441" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1441">
+        <v>0</v>
+      </c>
+      <c r="E1441">
+        <v>0</v>
+      </c>
+      <c r="F1441">
+        <v>0</v>
+      </c>
+      <c r="G1441">
+        <v>0</v>
+      </c>
+      <c r="H1441">
+        <v>0</v>
+      </c>
+      <c r="I1441" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1442" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1442">
+        <v>0</v>
+      </c>
+      <c r="E1442">
+        <v>0</v>
+      </c>
+      <c r="F1442">
+        <v>0</v>
+      </c>
+      <c r="G1442">
+        <v>0</v>
+      </c>
+      <c r="H1442">
+        <v>0</v>
+      </c>
+      <c r="I1442" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1443" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1443">
+        <v>0</v>
+      </c>
+      <c r="E1443">
+        <v>0</v>
+      </c>
+      <c r="F1443">
+        <v>0</v>
+      </c>
+      <c r="G1443">
+        <v>0</v>
+      </c>
+      <c r="H1443">
+        <v>0</v>
+      </c>
+      <c r="I1443" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1444" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1444">
+        <v>0</v>
+      </c>
+      <c r="E1444">
+        <v>0</v>
+      </c>
+      <c r="F1444">
+        <v>0</v>
+      </c>
+      <c r="G1444">
+        <v>0</v>
+      </c>
+      <c r="H1444">
+        <v>0</v>
+      </c>
+      <c r="I1444" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1445" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1445">
+        <v>0</v>
+      </c>
+      <c r="E1445">
+        <v>0</v>
+      </c>
+      <c r="F1445">
+        <v>0</v>
+      </c>
+      <c r="G1445">
+        <v>0</v>
+      </c>
+      <c r="H1445">
+        <v>0</v>
+      </c>
+      <c r="I1445" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1446" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1446">
+        <v>0</v>
+      </c>
+      <c r="E1446">
+        <v>0</v>
+      </c>
+      <c r="F1446">
+        <v>0</v>
+      </c>
+      <c r="G1446">
+        <v>0</v>
+      </c>
+      <c r="H1446">
+        <v>0</v>
+      </c>
+      <c r="I1446" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1447" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1447">
+        <v>0</v>
+      </c>
+      <c r="E1447">
+        <v>0</v>
+      </c>
+      <c r="F1447">
+        <v>0</v>
+      </c>
+      <c r="G1447">
+        <v>0</v>
+      </c>
+      <c r="H1447">
+        <v>0</v>
+      </c>
+      <c r="I1447" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1448" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1448">
+        <v>0</v>
+      </c>
+      <c r="E1448">
+        <v>0</v>
+      </c>
+      <c r="F1448">
+        <v>0</v>
+      </c>
+      <c r="G1448">
+        <v>0</v>
+      </c>
+      <c r="H1448">
+        <v>0</v>
+      </c>
+      <c r="I1448" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1449" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1449">
+        <v>0</v>
+      </c>
+      <c r="E1449">
+        <v>0</v>
+      </c>
+      <c r="F1449">
+        <v>0</v>
+      </c>
+      <c r="G1449">
+        <v>0</v>
+      </c>
+      <c r="H1449">
+        <v>0</v>
+      </c>
+      <c r="I1449" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1450" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1450">
+        <v>0</v>
+      </c>
+      <c r="E1450">
+        <v>0</v>
+      </c>
+      <c r="F1450">
+        <v>0</v>
+      </c>
+      <c r="G1450">
+        <v>0</v>
+      </c>
+      <c r="H1450">
+        <v>0</v>
+      </c>
+      <c r="I1450" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1451" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1451">
+        <v>0</v>
+      </c>
+      <c r="E1451">
+        <v>0</v>
+      </c>
+      <c r="F1451">
+        <v>0</v>
+      </c>
+      <c r="G1451">
+        <v>0</v>
+      </c>
+      <c r="H1451">
+        <v>0</v>
+      </c>
+      <c r="I1451" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1452" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1452">
+        <v>0</v>
+      </c>
+      <c r="E1452">
+        <v>0</v>
+      </c>
+      <c r="F1452">
+        <v>0</v>
+      </c>
+      <c r="G1452">
+        <v>0</v>
+      </c>
+      <c r="H1452">
+        <v>0</v>
+      </c>
+      <c r="I1452" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1453" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1453">
+        <v>0</v>
+      </c>
+      <c r="E1453">
+        <v>0</v>
+      </c>
+      <c r="F1453">
+        <v>0</v>
+      </c>
+      <c r="G1453">
+        <v>0</v>
+      </c>
+      <c r="H1453">
+        <v>0</v>
+      </c>
+      <c r="I1453" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1454" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1454">
+        <v>0</v>
+      </c>
+      <c r="E1454">
+        <v>0</v>
+      </c>
+      <c r="F1454">
+        <v>0</v>
+      </c>
+      <c r="G1454">
+        <v>0</v>
+      </c>
+      <c r="H1454">
+        <v>0</v>
+      </c>
+      <c r="I1454" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1455" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1455">
+        <v>0</v>
+      </c>
+      <c r="E1455">
+        <v>0</v>
+      </c>
+      <c r="F1455">
+        <v>0</v>
+      </c>
+      <c r="G1455">
+        <v>0</v>
+      </c>
+      <c r="H1455">
+        <v>0</v>
+      </c>
+      <c r="I1455" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1456" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1456">
+        <v>0</v>
+      </c>
+      <c r="E1456">
+        <v>0</v>
+      </c>
+      <c r="F1456">
+        <v>0</v>
+      </c>
+      <c r="G1456">
+        <v>0</v>
+      </c>
+      <c r="H1456">
+        <v>0</v>
+      </c>
+      <c r="I1456" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1457" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1457">
+        <v>0</v>
+      </c>
+      <c r="E1457">
+        <v>0</v>
+      </c>
+      <c r="F1457">
+        <v>0</v>
+      </c>
+      <c r="G1457">
+        <v>0</v>
+      </c>
+      <c r="H1457">
+        <v>0</v>
+      </c>
+      <c r="I1457" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1458" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1458">
+        <v>0</v>
+      </c>
+      <c r="E1458">
+        <v>0</v>
+      </c>
+      <c r="F1458">
+        <v>0</v>
+      </c>
+      <c r="G1458">
+        <v>0</v>
+      </c>
+      <c r="H1458">
+        <v>0</v>
+      </c>
+      <c r="I1458" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1459" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1459">
+        <v>0</v>
+      </c>
+      <c r="E1459">
+        <v>0</v>
+      </c>
+      <c r="F1459">
+        <v>0</v>
+      </c>
+      <c r="G1459">
+        <v>0</v>
+      </c>
+      <c r="H1459">
+        <v>0</v>
+      </c>
+      <c r="I1459" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1460" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1460">
+        <v>0</v>
+      </c>
+      <c r="E1460">
+        <v>0</v>
+      </c>
+      <c r="F1460">
+        <v>0</v>
+      </c>
+      <c r="G1460">
+        <v>0</v>
+      </c>
+      <c r="H1460">
+        <v>0</v>
+      </c>
+      <c r="I1460" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1461" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1461">
+        <v>0</v>
+      </c>
+      <c r="E1461">
+        <v>0</v>
+      </c>
+      <c r="F1461">
+        <v>0</v>
+      </c>
+      <c r="G1461">
+        <v>0</v>
+      </c>
+      <c r="H1461">
+        <v>0</v>
+      </c>
+      <c r="I1461" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1462" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1462">
+        <v>0</v>
+      </c>
+      <c r="E1462">
+        <v>0</v>
+      </c>
+      <c r="F1462">
+        <v>0</v>
+      </c>
+      <c r="G1462">
+        <v>0</v>
+      </c>
+      <c r="H1462">
+        <v>0</v>
+      </c>
+      <c r="I1462" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1463" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1463">
+        <v>0</v>
+      </c>
+      <c r="E1463">
+        <v>0</v>
+      </c>
+      <c r="F1463">
+        <v>0</v>
+      </c>
+      <c r="G1463">
+        <v>0</v>
+      </c>
+      <c r="H1463">
+        <v>0</v>
+      </c>
+      <c r="I1463" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1464" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1464">
+        <v>0</v>
+      </c>
+      <c r="E1464">
+        <v>0</v>
+      </c>
+      <c r="F1464">
+        <v>0</v>
+      </c>
+      <c r="G1464">
+        <v>0</v>
+      </c>
+      <c r="H1464">
+        <v>0</v>
+      </c>
+      <c r="I1464" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1465" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1465">
+        <v>0</v>
+      </c>
+      <c r="E1465">
+        <v>0</v>
+      </c>
+      <c r="F1465">
+        <v>0</v>
+      </c>
+      <c r="G1465">
+        <v>0</v>
+      </c>
+      <c r="H1465">
+        <v>0</v>
+      </c>
+      <c r="I1465" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1466" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1466">
+        <v>0</v>
+      </c>
+      <c r="E1466">
+        <v>0</v>
+      </c>
+      <c r="F1466">
+        <v>0</v>
+      </c>
+      <c r="G1466">
+        <v>0</v>
+      </c>
+      <c r="H1466">
+        <v>0</v>
+      </c>
+      <c r="I1466" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1467" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1467">
+        <v>0</v>
+      </c>
+      <c r="E1467">
+        <v>0</v>
+      </c>
+      <c r="F1467">
+        <v>0</v>
+      </c>
+      <c r="G1467">
+        <v>0</v>
+      </c>
+      <c r="H1467">
+        <v>0</v>
+      </c>
+      <c r="I1467" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1468" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1468">
+        <v>0</v>
+      </c>
+      <c r="E1468">
+        <v>0</v>
+      </c>
+      <c r="F1468">
+        <v>0</v>
+      </c>
+      <c r="G1468">
+        <v>0</v>
+      </c>
+      <c r="H1468">
+        <v>0</v>
+      </c>
+      <c r="I1468" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1469" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1469">
+        <v>0</v>
+      </c>
+      <c r="E1469">
+        <v>0</v>
+      </c>
+      <c r="F1469">
+        <v>0</v>
+      </c>
+      <c r="G1469">
+        <v>0</v>
+      </c>
+      <c r="H1469">
+        <v>0</v>
+      </c>
+      <c r="I1469" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1470" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1470">
+        <v>0</v>
+      </c>
+      <c r="E1470">
+        <v>0</v>
+      </c>
+      <c r="F1470">
+        <v>0</v>
+      </c>
+      <c r="G1470">
+        <v>0</v>
+      </c>
+      <c r="H1470">
+        <v>0</v>
+      </c>
+      <c r="I1470" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1471" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1471">
+        <v>0</v>
+      </c>
+      <c r="E1471">
+        <v>0</v>
+      </c>
+      <c r="F1471">
+        <v>0</v>
+      </c>
+      <c r="G1471">
+        <v>0</v>
+      </c>
+      <c r="H1471">
+        <v>0</v>
+      </c>
+      <c r="I1471" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1472" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1472">
+        <v>0</v>
+      </c>
+      <c r="E1472">
+        <v>0</v>
+      </c>
+      <c r="F1472">
+        <v>0</v>
+      </c>
+      <c r="G1472">
+        <v>0</v>
+      </c>
+      <c r="H1472">
+        <v>0</v>
+      </c>
+      <c r="I1472" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1473" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1473">
+        <v>0</v>
+      </c>
+      <c r="E1473">
+        <v>0</v>
+      </c>
+      <c r="F1473">
+        <v>0</v>
+      </c>
+      <c r="G1473">
+        <v>0</v>
+      </c>
+      <c r="H1473">
+        <v>0</v>
+      </c>
+      <c r="I1473" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1474" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1474">
+        <v>0</v>
+      </c>
+      <c r="E1474">
+        <v>0</v>
+      </c>
+      <c r="F1474">
+        <v>0</v>
+      </c>
+      <c r="G1474">
+        <v>0</v>
+      </c>
+      <c r="H1474">
+        <v>0</v>
+      </c>
+      <c r="I1474" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1475" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1475">
+        <v>77</v>
+      </c>
+      <c r="E1475">
+        <v>1</v>
+      </c>
+      <c r="F1475">
+        <v>24.8</v>
+      </c>
+      <c r="G1475">
+        <v>0</v>
+      </c>
+      <c r="H1475">
+        <v>0</v>
+      </c>
+      <c r="I1475" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1476" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1476">
+        <v>439</v>
+      </c>
+      <c r="E1476">
+        <v>17</v>
+      </c>
+      <c r="F1476">
+        <v>358.57</v>
+      </c>
+      <c r="G1476">
+        <v>4630.51</v>
+      </c>
+      <c r="H1476">
+        <v>2</v>
+      </c>
+      <c r="I1476" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1477" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1477">
+        <v>967</v>
+      </c>
+      <c r="E1477">
+        <v>29</v>
+      </c>
+      <c r="F1477">
+        <v>387.1</v>
+      </c>
+      <c r="G1477">
+        <v>1778.82</v>
+      </c>
+      <c r="H1477">
+        <v>1</v>
+      </c>
+      <c r="I1477" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1478" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1478">
+        <v>1751</v>
+      </c>
+      <c r="E1478">
+        <v>40</v>
+      </c>
+      <c r="F1478">
+        <v>569.91999999999996</v>
+      </c>
+      <c r="G1478">
+        <v>1778.81</v>
+      </c>
+      <c r="H1478">
+        <v>1</v>
+      </c>
+      <c r="I1478" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1479" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1479">
+        <v>1400</v>
+      </c>
+      <c r="E1479">
+        <v>27</v>
+      </c>
+      <c r="F1479">
+        <v>473.22</v>
+      </c>
+      <c r="G1479">
+        <v>1778.81</v>
+      </c>
+      <c r="H1479">
+        <v>1</v>
+      </c>
+      <c r="I1479" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1480" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1480">
+        <v>1286</v>
+      </c>
+      <c r="E1480">
+        <v>33</v>
+      </c>
+      <c r="F1480">
+        <v>625.66</v>
+      </c>
+      <c r="G1480">
+        <v>0</v>
+      </c>
+      <c r="H1480">
+        <v>0</v>
+      </c>
+      <c r="I1480" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1481" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1481">
+        <v>0</v>
+      </c>
+      <c r="E1481">
+        <v>0</v>
+      </c>
+      <c r="F1481">
+        <v>0</v>
+      </c>
+      <c r="G1481">
+        <v>0</v>
+      </c>
+      <c r="H1481">
+        <v>0</v>
+      </c>
+      <c r="I1481" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1482" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1482">
+        <v>0</v>
+      </c>
+      <c r="E1482">
+        <v>0</v>
+      </c>
+      <c r="F1482">
+        <v>0</v>
+      </c>
+      <c r="G1482">
+        <v>0</v>
+      </c>
+      <c r="H1482">
+        <v>0</v>
+      </c>
+      <c r="I1482" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1483" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1483">
+        <v>0</v>
+      </c>
+      <c r="E1483">
+        <v>0</v>
+      </c>
+      <c r="F1483">
+        <v>0</v>
+      </c>
+      <c r="G1483">
+        <v>0</v>
+      </c>
+      <c r="H1483">
+        <v>0</v>
+      </c>
+      <c r="I1483" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1484" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1484">
+        <v>0</v>
+      </c>
+      <c r="E1484">
+        <v>0</v>
+      </c>
+      <c r="F1484">
+        <v>0</v>
+      </c>
+      <c r="G1484">
+        <v>0</v>
+      </c>
+      <c r="H1484">
+        <v>0</v>
+      </c>
+      <c r="I1484" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1485" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1485">
+        <v>0</v>
+      </c>
+      <c r="E1485">
+        <v>0</v>
+      </c>
+      <c r="F1485">
+        <v>0</v>
+      </c>
+      <c r="G1485">
+        <v>0</v>
+      </c>
+      <c r="H1485">
+        <v>0</v>
+      </c>
+      <c r="I1485" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1486" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1486">
+        <v>0</v>
+      </c>
+      <c r="E1486">
+        <v>0</v>
+      </c>
+      <c r="F1486">
+        <v>0</v>
+      </c>
+      <c r="G1486">
+        <v>0</v>
+      </c>
+      <c r="H1486">
+        <v>0</v>
+      </c>
+      <c r="I1486" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1487" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1487">
+        <v>0</v>
+      </c>
+      <c r="E1487">
+        <v>0</v>
+      </c>
+      <c r="F1487">
+        <v>0</v>
+      </c>
+      <c r="G1487">
+        <v>0</v>
+      </c>
+      <c r="H1487">
+        <v>0</v>
+      </c>
+      <c r="I1487" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1488" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1488">
+        <v>3377</v>
+      </c>
+      <c r="E1488">
+        <v>144</v>
+      </c>
+      <c r="F1488">
+        <v>1712.06</v>
+      </c>
+      <c r="G1488">
+        <v>0</v>
+      </c>
+      <c r="H1488">
+        <v>0</v>
+      </c>
+      <c r="I1488" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1489" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1489">
+        <v>2403</v>
+      </c>
+      <c r="E1489">
+        <v>106</v>
+      </c>
+      <c r="F1489">
+        <v>1217.5</v>
+      </c>
+      <c r="G1489">
+        <v>5931.36</v>
+      </c>
+      <c r="H1489">
+        <v>2</v>
+      </c>
+      <c r="I1489" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1490" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1490">
+        <v>2454</v>
+      </c>
+      <c r="E1490">
+        <v>127</v>
+      </c>
+      <c r="F1490">
+        <v>1745.21</v>
+      </c>
+      <c r="G1490">
+        <v>10167.799999999999</v>
+      </c>
+      <c r="H1490">
+        <v>2</v>
+      </c>
+      <c r="I1490" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1491" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1491">
+        <v>2021</v>
+      </c>
+      <c r="E1491">
+        <v>98</v>
+      </c>
+      <c r="F1491">
+        <v>959.65</v>
+      </c>
+      <c r="G1491">
+        <v>0</v>
+      </c>
+      <c r="H1491">
+        <v>0</v>
+      </c>
+      <c r="I1491" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1492" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1492">
+        <v>1889</v>
+      </c>
+      <c r="E1492">
+        <v>99</v>
+      </c>
+      <c r="F1492">
+        <v>878.34</v>
+      </c>
+      <c r="G1492">
+        <v>7539.83</v>
+      </c>
+      <c r="H1492">
+        <v>2</v>
+      </c>
+      <c r="I1492" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1493" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1493">
+        <v>1238</v>
+      </c>
+      <c r="E1493">
+        <v>65</v>
+      </c>
+      <c r="F1493">
+        <v>607.58000000000004</v>
+      </c>
+      <c r="G1493">
+        <v>2456.7800000000002</v>
+      </c>
+      <c r="H1493">
+        <v>1</v>
+      </c>
+      <c r="I1493" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1494" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1494">
+        <v>1872</v>
+      </c>
+      <c r="E1494">
+        <v>104</v>
+      </c>
+      <c r="F1494">
+        <v>832.53</v>
+      </c>
+      <c r="G1494">
+        <v>12856.78</v>
+      </c>
+      <c r="H1494">
+        <v>4</v>
+      </c>
+      <c r="I1494" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1495" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1495">
+        <v>0</v>
+      </c>
+      <c r="E1495">
+        <v>0</v>
+      </c>
+      <c r="F1495">
+        <v>0</v>
+      </c>
+      <c r="G1495">
+        <v>0</v>
+      </c>
+      <c r="H1495">
+        <v>0</v>
+      </c>
+      <c r="I1495" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1496" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1496">
+        <v>0</v>
+      </c>
+      <c r="E1496">
+        <v>0</v>
+      </c>
+      <c r="F1496">
+        <v>0</v>
+      </c>
+      <c r="G1496">
+        <v>0</v>
+      </c>
+      <c r="H1496">
+        <v>0</v>
+      </c>
+      <c r="I1496" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1497" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1497">
+        <v>0</v>
+      </c>
+      <c r="E1497">
+        <v>0</v>
+      </c>
+      <c r="F1497">
+        <v>0</v>
+      </c>
+      <c r="G1497">
+        <v>0</v>
+      </c>
+      <c r="H1497">
+        <v>0</v>
+      </c>
+      <c r="I1497" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1498" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1498">
+        <v>0</v>
+      </c>
+      <c r="E1498">
+        <v>0</v>
+      </c>
+      <c r="F1498">
+        <v>0</v>
+      </c>
+      <c r="G1498">
+        <v>0</v>
+      </c>
+      <c r="H1498">
+        <v>0</v>
+      </c>
+      <c r="I1498" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1499" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1499">
+        <v>0</v>
+      </c>
+      <c r="E1499">
+        <v>0</v>
+      </c>
+      <c r="F1499">
+        <v>0</v>
+      </c>
+      <c r="G1499">
+        <v>0</v>
+      </c>
+      <c r="H1499">
+        <v>0</v>
+      </c>
+      <c r="I1499" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1500" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1500">
+        <v>0</v>
+      </c>
+      <c r="E1500">
+        <v>0</v>
+      </c>
+      <c r="F1500">
+        <v>0</v>
+      </c>
+      <c r="G1500">
+        <v>0</v>
+      </c>
+      <c r="H1500">
+        <v>0</v>
+      </c>
+      <c r="I1500" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1501" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1501">
+        <v>0</v>
+      </c>
+      <c r="E1501">
+        <v>0</v>
+      </c>
+      <c r="F1501">
+        <v>0</v>
+      </c>
+      <c r="G1501">
+        <v>0</v>
+      </c>
+      <c r="H1501">
+        <v>0</v>
+      </c>
+      <c r="I1501" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/ams_weekly_data/Nexlev/ads_report_week10.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week10.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6633,4 +6634,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>